--- a/SSA_upgrade/SSA Upgrade Project Cost V1.xlsx
+++ b/SSA_upgrade/SSA Upgrade Project Cost V1.xlsx
@@ -6,8 +6,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="8460" yWindow="5385" windowWidth="20955" windowHeight="16425" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cover page" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SSA quote from R&amp;K" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class 4 Estimate" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cover page" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SSA quote from R&amp;K" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -16,8 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.0"/>
+  </numFmts>
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,16 +40,76 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E2F3"/>
+        <bgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6B8B7"/>
+        <bgColor rgb="00E6B8B7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -69,11 +132,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="2"/>
@@ -87,6 +156,19 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -430,6 +512,1877 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H84"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>SPEAR3 SSA Upgrade Project - Class 4 Cost Estimate (AACE 18R-97)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Design Maturity: 5-15%  |  Labor Rate: $200/hr burdened  |  1 FTE = 1,740 hrs/yr  |  All costs in k$  |  Base year: 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>WBS</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>M&amp;S (k$)</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Labor (FTE)</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Labor (k$)</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Total (k$)</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>Conf.</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>Basis of Estimate / Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>SSA RF SOURCE</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="n"/>
+      <c r="D6" s="10" t="n"/>
+      <c r="E6" s="10" t="n"/>
+      <c r="F6" s="10" t="n"/>
+      <c r="G6" s="10" t="n"/>
+      <c r="H6" s="10" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>SSA Modules (16 x 65 kW, R&amp;K Company)</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>4985.6</v>
+      </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n">
+        <v>4985.6</v>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>R&amp;K quote July 2025: $311,600/unit x 16 = $4,985,600. 476.3 MHz CW. Includes internal PS, LCW cooling, VSWR protection, Ethernet/serial control.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>SSA Spare Modules (2 units)</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>623.2</v>
+      </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n">
+        <v>623.2</v>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>2 hot-swap spares @ $311,600 each. Industry practice for 16-module system. Enables rapid module replacement without waiting for vendor lead time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>SSA Design Study &amp; Prototype Test</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="n"/>
+      <c r="D9" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>348</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>348</v>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>0.5 FTE prototype design + 0.5 FTE vendor collaboration and test iteration. Includes acceptance test protocol development. Per cover page row 7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>SSA Test Stand (Bldg 122)</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E10" s="11" t="n">
+        <v>174</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>249</v>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>High-power RF load (50 kW CW), power measurement, 480V service, LCW (~15 GPM per 3/10 mtg). Existing Bldg 122 LCW connection usable. 0.5 FTE setup/integration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr"/>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Subtotal WBS 1.0</t>
+        </is>
+      </c>
+      <c r="C11" s="12">
+        <f>SUM(C7:C10)</f>
+        <v/>
+      </c>
+      <c r="D11" s="12" t="n"/>
+      <c r="E11" s="12">
+        <f>SUM(E7:E10)</f>
+        <v/>
+      </c>
+      <c r="F11" s="12">
+        <f>SUM(F7:F10)</f>
+        <v/>
+      </c>
+      <c r="G11" s="12" t="n"/>
+      <c r="H11" s="12" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>RF DISTRIBUTION &amp; COMBINING</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="10" t="n"/>
+      <c r="H13" s="10" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>6-1/8" Coaxial Combiners (4 x 4:1)</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="n">
+        <v>160</v>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E14" s="11" t="n">
+        <v>87</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>247</v>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>4 combiners, each combining 4 SSA outputs (6-1/8" coax) into single WR2100 port. ~$40k each installed. Each SSA cabinet outputs 6-1/8" coax per 3/10 mtg notes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>WR2100 Waveguide Runs (4 independent)</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>300</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>174</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>474</v>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>4 independent WR2100 runs from SSA bldg to 4 cavities. Straight sections, H/E-plane bends, flex sections. ~10 lb/ft, Unistrut hangers every 8 ft. Lambda_g=80.4 cm at 476.3 MHz; lengths matched to +/- n*lambda_g.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Circulators (4 x 250+ kW @ 476 MHz)</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>400</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>452.2</v>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>4 ferrite circulators, one per combined output. $80-120k each NEW. NOTE: PEP-II 1.5 MW circulators available (per 2/24 mtg) - if reusable, M&amp;S drops to ~$0. Carry new-buy as baseline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>RF Loads (circulator loads, terminations)</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="D17" s="11" t="n"/>
+      <c r="E17" s="11" t="n"/>
+      <c r="F17" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>4 circulator loads (water-cooled, ~250 kW each), waveguide terminations, dummy loads for commissioning. Loads cooled by HCW (separate from LCW per 3/10 mtg).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Directional Couplers &amp; Transitions</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="11" t="n"/>
+      <c r="F18" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>Directional couplers at each combined output (4) and at each SSA output (16 may be internal). WR2100-to-coax transitions. Phase trimmers for combining efficiency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Waveguide Supports, Hangers, Hardware</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>87</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>137</v>
+      </c>
+      <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>Unistrut channel, beam clamps, waveguide hangers every 8 ft, mounting hardware. Some supports from equipment platform structure above (per 3/10 mtg).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr"/>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>Subtotal WBS 2.0</t>
+        </is>
+      </c>
+      <c r="C20" s="12">
+        <f>SUM(C14:C19)</f>
+        <v/>
+      </c>
+      <c r="D20" s="12" t="n"/>
+      <c r="E20" s="12">
+        <f>SUM(E14:E19)</f>
+        <v/>
+      </c>
+      <c r="F20" s="12">
+        <f>SUM(F14:F19)</f>
+        <v/>
+      </c>
+      <c r="G20" s="12" t="n"/>
+      <c r="H20" s="12" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>CONTROL ELECTRONICS</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="10" t="n"/>
+      <c r="G22" s="10" t="n"/>
+      <c r="H22" s="10" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>LLRF9 Controllers (4 x Dimtel LLRF9/500)</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="n">
+        <v>398</v>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>174</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>572</v>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="H23" s="11" t="inlineStr">
+        <is>
+          <t>Dimtel LLRF9/500 list $117k; 15% vol discount = $99.45k each x 4 = $397.8k. Each unit: 9 RF channels, FPGA interlocks &lt;1us, built-in EPICS IOC, 10 Hz scalar readback. 0.5 FTE for integration/configuration. Per LLRFUpgradeTaskListRev3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>Interface Chassis (SSA topology)</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E24" s="11" t="n">
+        <v>261</v>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>286</v>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>Central interlock hub: AND-logic, first-fault latching, fiber-optic HVPS ctrl, &lt;1us response. SSA version needs per-station permit logic + module-level status. PCB design + fabrication + chassis. CRITICAL PATH per 0_SYSTEM_DESIGN_REPORT.md Sec 8.3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>RF MPS PLC (ControlLogix 1756)</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>174</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>204</v>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>AB ControlLogix PLC: $22k/set (detailed BOM in TaskListRev3: 5069-L320ER $3.7k, OF8 $1.5k x3, OX41 $451 x10, etc). SSA needs expanded I/O for 16 modules. +$8k for additional I/O modules. 0.5 FTE PLC programming + EPICS IOC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>Arc Detection System</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>124.4</v>
+      </c>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>Microstep-MIS sensors 470EUR x10=$5.1k, receivers 635EUR x6=$4.1k, cables=$1.1k, DB25=$200, mech adapters=$7k. Per TaskListRev3 quote from Erik Bystricky Nov 2024. 10 sensors (8 cavity + 1 kly + 1 circ), 5+1 receivers. Arc Detection Chassis: OR-gate + 10-bit latch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>Waveform Buffer System</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>174</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>189</v>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>Custom chassis: 8 RF + 4 HVPS channels, circular buffers, analog comparator trips, enhanced collector power protection algorithm. MCL ZX47-40LN-S+ detectors ($1.7k) + signal conditioning opamps + ADCs + chassis. Per WaveformBuffersforLLRFUpgrade.docx (Sebek, Jan 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>SSA Module Status Monitoring</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E28" s="11" t="n">
+        <v>87</v>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>102</v>
+      </c>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>Per-module monitoring: VSWR, output power, temperature, fault status x16 modules. Ethernet/serial polling + analog readback. May be integrated into MPS PLC I/O or dedicated monitoring chassis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>Tuner Motor Controllers (4 x Galil DMC-4143)</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>114.4</v>
+      </c>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>Galil DMC-4143 4-axis controller $1,675 each x2 (1 operational + 1 spare). Motor drivers, cables, encoder interfaces. EPICS motor record support. Per galil/ commissioning docs. RISK: reliability TBD - test on booster tuners first (Sec 10.6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>PPS Interface Box</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E30" s="11" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>Small Bud enclosure ~6x5x4in, 4 relays, status LEDs, inhibit buttons. Proven design per Ben Morris 3/5/2026 (pps_Ben.md). Identical to gallery/6575 modulator systems. Requires PPS group review and RSWCF. $2-5k materials.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>Cables, Connectors, Integration Materials</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="D31" s="11" t="n"/>
+      <c r="E31" s="11" t="n"/>
+      <c r="F31" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>RF cables (SMA, Type-N), fiber optic links (HFBR-1412/2412), LEMO interlock cables, multi-conductor digital cables, power supplies, rack hardware, PDUs, labels. ~10% of WBS 3.1-3.8 hardware.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr"/>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>Subtotal WBS 3.0</t>
+        </is>
+      </c>
+      <c r="C32" s="12">
+        <f>SUM(C23:C31)</f>
+        <v/>
+      </c>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="12">
+        <f>SUM(E23:E31)</f>
+        <v/>
+      </c>
+      <c r="F32" s="12">
+        <f>SUM(F23:F31)</f>
+        <v/>
+      </c>
+      <c r="G32" s="12" t="n"/>
+      <c r="H32" s="12" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>SOFTWARE &amp; INTEGRATION</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="10" t="n"/>
+      <c r="G34" s="10" t="n"/>
+      <c r="H34" s="10" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>EPICS IOC Development</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D35" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E35" s="11" t="n">
+        <v>261</v>
+      </c>
+      <c r="F35" s="11" t="n">
+        <v>271</v>
+      </c>
+      <c r="G35" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H35" s="11" t="inlineStr">
+        <is>
+          <t>IOCs for: LLRF9 (Dimtel provides baseline, SPEAR customization), MPS ControlLogix (EtherIP/pycomm3), SSA module monitoring (ASYN/StreamDevice), Waveform Buffer, Chroma heater ASYN driver. Dev tools + test licenses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>State Machine / EPICS Coordinator</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="n"/>
+      <c r="D36" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="11" t="n">
+        <v>348</v>
+      </c>
+      <c r="F36" s="11" t="n">
+        <v>348</v>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>Python/MATLAB supervisory control ~1 Hz. States: OFF/PARK/TUNE/ON_CW. Fault handling, auto-recovery, HVPS ramp control, heater warm-up/cooldown sequences. Load angle offset loop (balance 4 cavity fields). CRITICAL: largest untouched software scope per Sec 19.3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>Operator Interface (EDM/CSS Panels)</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="n"/>
+      <c r="D37" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>87</v>
+      </c>
+      <c r="F37" s="11" t="n">
+        <v>87</v>
+      </c>
+      <c r="G37" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>EDM/CSS operator displays: station overview, per-module SSA status, LLRF9 summary, MPS fault tree, waveform displays, tuner positions, HVPS status. Based on existing rf_station_4CVSPR.edl pattern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>Commissioning Tools &amp; Scripts</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D38" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E38" s="11" t="n">
+        <v>87</v>
+      </c>
+      <c r="F38" s="11" t="n">
+        <v>92</v>
+      </c>
+      <c r="G38" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H38" s="11" t="inlineStr">
+        <is>
+          <t>MATLAB/Python tools for: SSA phase calibration, combiner efficiency optimization, interlock chain verification, automated fault injection testing, performance logging. Per legacy rf_calib.st (2,800+ lines).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Documentation &amp; Training</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="n"/>
+      <c r="D39" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E39" s="11" t="n">
+        <v>87</v>
+      </c>
+      <c r="F39" s="11" t="n">
+        <v>87</v>
+      </c>
+      <c r="G39" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H39" s="11" t="inlineStr">
+        <is>
+          <t>System documentation, as-built drawings, operator training materials, maintenance procedures. ~25 schematics for MPS + ~25 for HVPS (per TaskListRev3). Training for operations staff on new SSA system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr"/>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>Subtotal WBS 4.0</t>
+        </is>
+      </c>
+      <c r="C40" s="12">
+        <f>SUM(C35:C39)</f>
+        <v/>
+      </c>
+      <c r="D40" s="12" t="n"/>
+      <c r="E40" s="12">
+        <f>SUM(E35:E39)</f>
+        <v/>
+      </c>
+      <c r="F40" s="12">
+        <f>SUM(F35:F39)</f>
+        <v/>
+      </c>
+      <c r="G40" s="12" t="n"/>
+      <c r="H40" s="12" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>INSTALLATION &amp; COMMISSIONING</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="n"/>
+      <c r="D42" s="10" t="n"/>
+      <c r="E42" s="10" t="n"/>
+      <c r="F42" s="10" t="n"/>
+      <c r="G42" s="10" t="n"/>
+      <c r="H42" s="10" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>SSA Module Installation (4 stations)</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D43" s="11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E43" s="11" t="n">
+        <v>480</v>
+      </c>
+      <c r="F43" s="11" t="n">
+        <v>530</v>
+      </c>
+      <c r="G43" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>4 person-3 weeks/station x 4 stations = 12 person-months. Rack mounting, 480V power connections, LCW plumbing to each module, RF output cabling, control/interlock wiring. $50k for tools, rigging, consumables. Per cover page row 8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>RF Distribution Installation</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D44" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E44" s="11" t="n">
+        <v>261</v>
+      </c>
+      <c r="F44" s="11" t="n">
+        <v>291</v>
+      </c>
+      <c r="G44" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H44" s="11" t="inlineStr">
+        <is>
+          <t>Waveguide assembly, circulator installation (vertical orientation per 2/24 mtg), combiner hookup, load installation. Requires crane for heavy components. Waveguide alignment and RF leak testing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>Controls &amp; Cabling Installation</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D45" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E45" s="11" t="n">
+        <v>174</v>
+      </c>
+      <c r="F45" s="11" t="n">
+        <v>194</v>
+      </c>
+      <c r="G45" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H45" s="11" t="inlineStr">
+        <is>
+          <t>LLRF9 rack mounting, MPS PLC wiring, Interface Chassis installation, arc detector fiber routing, interlock cabling, Ethernet network, fiber-optic links to HVPS (HFBR-1412/2412).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>System Integration Testing</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="n"/>
+      <c r="D46" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E46" s="11" t="n">
+        <v>174</v>
+      </c>
+      <c r="F46" s="11" t="n">
+        <v>174</v>
+      </c>
+      <c r="G46" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H46" s="11" t="inlineStr">
+        <is>
+          <t>End-to-end interlock chain testing (Layer 1-4), EPICS PV verification, fault injection testing, waveform capture validation. Limited window due to SPEAR operations (per Sec 19.1 constraint).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>Phased Commissioning (per-station turn-on)</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D47" s="11" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E47" s="11" t="n">
+        <v>240</v>
+      </c>
+      <c r="F47" s="11" t="n">
+        <v>260</v>
+      </c>
+      <c r="G47" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H47" s="11" t="inlineStr">
+        <is>
+          <t>6 person-2 months commissioning (per cover page row 8). Incremental power ramp per station. Performance validation: amplitude stability &lt;0.1%, phase &lt;0.1 deg. Includes Dimtel 1-week on-site support per LLRF9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr"/>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>Subtotal WBS 5.0</t>
+        </is>
+      </c>
+      <c r="C48" s="12">
+        <f>SUM(C43:C47)</f>
+        <v/>
+      </c>
+      <c r="D48" s="12" t="n"/>
+      <c r="E48" s="12">
+        <f>SUM(E43:E47)</f>
+        <v/>
+      </c>
+      <c r="F48" s="12">
+        <f>SUM(F43:F47)</f>
+        <v/>
+      </c>
+      <c r="G48" s="12" t="n"/>
+      <c r="H48" s="12" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>SITE PREPARATION &amp; REMOVAL</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="n"/>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="10" t="n"/>
+      <c r="F50" s="10" t="n"/>
+      <c r="G50" s="10" t="n"/>
+      <c r="H50" s="10" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t>Existing Waveguide Removal</t>
+        </is>
+      </c>
+      <c r="C51" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D51" s="11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E51" s="11" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="F51" s="11" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="G51" s="11" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="H51" s="11" t="inlineStr">
+        <is>
+          <t>Remove existing klystron waveguide (magic tee splitters, existing WR2100 run). Roof waveguide splitters removed; direct 1:1 SSA-to-cavity runs replace them (per 2/24 mtg).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t>Cable Tray Relocation</t>
+        </is>
+      </c>
+      <c r="C52" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D52" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E52" s="11" t="n">
+        <v>87</v>
+      </c>
+      <c r="F52" s="11" t="n">
+        <v>97</v>
+      </c>
+      <c r="G52" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H52" s="11" t="inlineStr">
+        <is>
+          <t>Straighten S-shaped cable trays for 4 waveguide runs on roof (per 2/24 mtg). Relocate cable trays between 118 and ring ~10 ft outward for clearance. 4 person-1 month per cover page row 9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t>Equipment Relocation</t>
+        </is>
+      </c>
+      <c r="C53" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D53" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E53" s="11" t="n">
+        <v>87</v>
+      </c>
+      <c r="F53" s="11" t="n">
+        <v>102</v>
+      </c>
+      <c r="G53" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H53" s="11" t="inlineStr">
+        <is>
+          <t>Relocate transformers (2-3), distribution panels, MPS controls cabinets during downtime. Remove old air-handler/chiller behind 507 (per 2/24 mtg). Relocate condensing unit 5-10 ft.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="inlineStr"/>
+      <c r="B54" s="12" t="inlineStr">
+        <is>
+          <t>Subtotal WBS 6.0</t>
+        </is>
+      </c>
+      <c r="C54" s="12">
+        <f>SUM(C51:C53)</f>
+        <v/>
+      </c>
+      <c r="D54" s="12" t="n"/>
+      <c r="E54" s="12">
+        <f>SUM(E51:E53)</f>
+        <v/>
+      </c>
+      <c r="F54" s="12">
+        <f>SUM(F51:F53)</f>
+        <v/>
+      </c>
+      <c r="G54" s="12" t="n"/>
+      <c r="H54" s="12" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>PROJECT MANAGEMENT</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="n"/>
+      <c r="D56" s="10" t="n"/>
+      <c r="E56" s="10" t="n"/>
+      <c r="F56" s="10" t="n"/>
+      <c r="G56" s="10" t="n"/>
+      <c r="H56" s="10" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t>Technical Program Management</t>
+        </is>
+      </c>
+      <c r="C57" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D57" s="11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E57" s="11" t="n">
+        <v>870</v>
+      </c>
+      <c r="F57" s="11" t="n">
+        <v>890</v>
+      </c>
+      <c r="G57" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H57" s="11" t="inlineStr">
+        <is>
+          <t>~0.5 FTE/yr average over ~5-year project. Schedule management, resource coordination, vendor management (R&amp;K, Dimtel), progress reporting. M&amp;S for travel to vendor sites, DOE reviews.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t>Safety Reviews &amp; PPS Coordination</t>
+        </is>
+      </c>
+      <c r="C58" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D58" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E58" s="11" t="n">
+        <v>174</v>
+      </c>
+      <c r="F58" s="11" t="n">
+        <v>184</v>
+      </c>
+      <c r="G58" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H58" s="11" t="inlineStr">
+        <is>
+          <t>PPS review/approval with SLAC AD Safety Division. LOTO procedures, arc flash analysis, OSHA compliance for building/stairway. Formal change control documentation, RSWCF. Early engagement critical (Sec 9.4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="inlineStr"/>
+      <c r="B59" s="12" t="inlineStr">
+        <is>
+          <t>Subtotal WBS 7.0</t>
+        </is>
+      </c>
+      <c r="C59" s="12">
+        <f>SUM(C57:C58)</f>
+        <v/>
+      </c>
+      <c r="D59" s="12" t="n"/>
+      <c r="E59" s="12">
+        <f>SUM(E57:E58)</f>
+        <v/>
+      </c>
+      <c r="F59" s="12">
+        <f>SUM(F57:F58)</f>
+        <v/>
+      </c>
+      <c r="G59" s="12" t="n"/>
+      <c r="H59" s="12" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="inlineStr">
+        <is>
+          <t>INFRASTRUCTURE (Reference - other groups may provide independent estimates)</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="n"/>
+      <c r="D61" s="10" t="n"/>
+      <c r="E61" s="10" t="n"/>
+      <c r="F61" s="10" t="n"/>
+      <c r="G61" s="10" t="n"/>
+      <c r="H61" s="10" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="13" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="B62" s="13" t="inlineStr">
+        <is>
+          <t>480 VAC Distribution System</t>
+        </is>
+      </c>
+      <c r="C62" s="13" t="n">
+        <v>900</v>
+      </c>
+      <c r="D62" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E62" s="13" t="n">
+        <v>696</v>
+      </c>
+      <c r="F62" s="13" t="n">
+        <v>1596</v>
+      </c>
+      <c r="G62" s="13" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H62" s="13" t="inlineStr">
+        <is>
+          <t>REFERENCE: Substation 507 option ($1-2M per 1/27 mtg). 2.5-3 MVA transformer 12kV-480V (~$150-200k); 12kV feed + switchgear (~$300k); 480V panels/breakers 4-8 buckets/SSA (~$200k); civil/cable (~$200k). F&amp;O/Andi scope. Alt: Sub 502 = $8-9M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="13" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="B63" s="13" t="inlineStr">
+        <is>
+          <t>Cooling Water (LCW/HCW)</t>
+        </is>
+      </c>
+      <c r="C63" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="D63" s="13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E63" s="13" t="n">
+        <v>522</v>
+      </c>
+      <c r="F63" s="13" t="n">
+        <v>772</v>
+      </c>
+      <c r="G63" s="13" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H63" s="13" t="inlineStr">
+        <is>
+          <t>REFERENCE: 400 GPM LCW for 4 SSA stations. Option B: new 6"+ connection to main header (per 3/10 mtg). 4"-&gt;6"+ piping upgrade ($100-150k); manifolds/valves/controls ($50-75k); HCW for loads ($25-50k). Javier/F&amp;O scope. Summer shutdown required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="13" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>Building Extension &amp; Mezzanine</t>
+        </is>
+      </c>
+      <c r="C64" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="D64" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E64" s="13" t="n">
+        <v>696</v>
+      </c>
+      <c r="F64" s="13" t="n">
+        <v>1196</v>
+      </c>
+      <c r="G64" s="13" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H64" s="13" t="inlineStr">
+        <is>
+          <t>REFERENCE: ~636 sqft extension + ~300 sqft mezzanine @ 27 ft. Two-story layout (per 2/24 mtg). OSHA stairway (~25 risers). Roll-up doors. HVAC for SSA heat. Seismic. F&amp;O prior test facility estimate: $1.3M (per 1/27 mtg). Javier/F&amp;O scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="12" t="inlineStr"/>
+      <c r="B65" s="12" t="inlineStr">
+        <is>
+          <t>Subtotal WBS 8.0 (Reference)</t>
+        </is>
+      </c>
+      <c r="C65" s="12">
+        <f>SUM(C62:C64)</f>
+        <v/>
+      </c>
+      <c r="D65" s="12" t="n"/>
+      <c r="E65" s="12">
+        <f>SUM(E62:E64)</f>
+        <v/>
+      </c>
+      <c r="F65" s="12">
+        <f>SUM(F62:F64)</f>
+        <v/>
+      </c>
+      <c r="G65" s="12" t="n"/>
+      <c r="H65" s="12" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="14" t="inlineStr"/>
+      <c r="B67" s="14" t="inlineStr">
+        <is>
+          <t>RF/CONTROLS SCOPE SUBTOTAL (WBS 1-7)</t>
+        </is>
+      </c>
+      <c r="C67" s="15">
+        <f>C11+C20+C32+C40+C48+C54+C59</f>
+        <v/>
+      </c>
+      <c r="D67" s="14" t="n"/>
+      <c r="E67" s="14">
+        <f>E11+E20+E32+E40+E48+E54+E59</f>
+        <v/>
+      </c>
+      <c r="F67" s="14">
+        <f>F11+F20+F32+F40+F48+F54+F59</f>
+        <v/>
+      </c>
+      <c r="G67" s="14" t="n"/>
+      <c r="H67" s="14" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="14" t="n"/>
+      <c r="B68" s="14" t="inlineStr">
+        <is>
+          <t>INFRASTRUCTURE REFERENCE (WBS 8)</t>
+        </is>
+      </c>
+      <c r="C68" s="14">
+        <f>C65</f>
+        <v/>
+      </c>
+      <c r="D68" s="14" t="n"/>
+      <c r="E68" s="14">
+        <f>E65</f>
+        <v/>
+      </c>
+      <c r="F68" s="14">
+        <f>F65</f>
+        <v/>
+      </c>
+      <c r="G68" s="14" t="n"/>
+      <c r="H68" s="14" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="16" t="n"/>
+      <c r="B69" s="16" t="inlineStr">
+        <is>
+          <t>PROJECT BASE ESTIMATE (WBS 1-8)</t>
+        </is>
+      </c>
+      <c r="C69" s="16">
+        <f>C67+C68</f>
+        <v/>
+      </c>
+      <c r="D69" s="16" t="n"/>
+      <c r="E69" s="16">
+        <f>E67+E68</f>
+        <v/>
+      </c>
+      <c r="F69" s="16">
+        <f>F67+F68</f>
+        <v/>
+      </c>
+      <c r="G69" s="16" t="n"/>
+      <c r="H69" s="16" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="14" t="inlineStr"/>
+      <c r="B71" s="14" t="inlineStr">
+        <is>
+          <t>CONTINGENCY (30% of base, per DOE 413.3B / AACE Class 4)</t>
+        </is>
+      </c>
+      <c r="C71" s="14" t="n"/>
+      <c r="D71" s="14" t="n"/>
+      <c r="E71" s="14" t="n"/>
+      <c r="F71" s="14">
+        <f>F69*0.30</f>
+        <v/>
+      </c>
+      <c r="G71" s="14" t="n"/>
+      <c r="H71" s="14" t="inlineStr">
+        <is>
+          <t>AACE 18R-97 Class 4: typical accuracy range -15% to +30%. DOE Order 413.3B requires contingency at conceptual design. 30% applied to full project base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="16" t="n"/>
+      <c r="B72" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL ESTIMATED COST (Base + Contingency)</t>
+        </is>
+      </c>
+      <c r="C72" s="16" t="n"/>
+      <c r="D72" s="16" t="n"/>
+      <c r="E72" s="16" t="n"/>
+      <c r="F72" s="16">
+        <f>F69+F71</f>
+        <v/>
+      </c>
+      <c r="G72" s="16" t="n"/>
+      <c r="H72" s="16" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="17" t="inlineStr">
+        <is>
+          <t>KEY ASSUMPTIONS &amp; RISKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Electrical based on Substation 507 option. Substation 502 option would add ~$7M to WBS 8.1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Circulator cost assumes new procurement. PEP-II 1.5 MW circulators may be reusable (saves ~$400k in WBS 2.3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>SSA spares (WBS 1.2) assume 2 units. Could be reduced to 1 (saves $312k) or increased per ops requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Labor rate: $200/hr burdened (SLAC lab rate including overhead). 1 FTE = 1,740 hrs/yr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>RISK: Interface Chassis on critical path (design not started). PCB iteration may add 3-6 months and $10-20k.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>RISK: Tuner motor controller reliability unproven. May require redesign (adds $20-50k and 0.5 FTE).</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>RISK: EPICS Coordinator software is largest untouched scope. Schedule risk if parallel development insufficient.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>RISK: PPS regulatory approval timeline uncertain. Early engagement with AD Safety Division required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>RISK: DOE lab construction costs typically 50-100% higher than commercial. WBS 8.3 may be significantly understated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>RISK: Limited SPEAR testing windows. Integration testing constrained to summer shutdowns and brief maintenance periods.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="B3:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -983,7 +2936,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/SSA_upgrade/SSA Upgrade Project Cost V1.xlsx
+++ b/SSA_upgrade/SSA Upgrade Project Cost V1.xlsx
@@ -6,9 +6,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="8460" yWindow="5385" windowWidth="20955" windowHeight="16425" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class 4 Estimate" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cover page" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SSA quote from R&amp;K" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project Scope" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class 4 Estimate" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Pricing" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cover page" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SSA quote from R&amp;K" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -20,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -69,6 +71,24 @@
     <font>
       <b val="1"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="00CC0000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="7">
@@ -142,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="2"/>
@@ -169,6 +189,12 @@
     <xf numFmtId="164" fontId="7" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -512,7 +538,619 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H84"/>
+  <dimension ref="A1:A102"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="90" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>SPEAR3 SSA Upgrade Project - Scope Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>1. PROJECT OBJECTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>Replace the existing single 1.2 MW klystron RF source at the SPEAR3 storage ring with a distributed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="21" t="inlineStr">
+        <is>
+          <t>solid-state amplifier (SSA) system consisting of 16 x 65 kW modules from R&amp;K Company (Japan),</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>delivering approximately 1,040 kW total RF power at 476.3 MHz to four RF cavities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>This project directly improves reliability (no single-point klystron failure), maintainability</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>(hot-swappable SSA modules), and operational flexibility (graceful degradation with N-1 capability).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>2. PREREQUISITE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>The LLRF upgrade project (separate scope, separately funded) must be completed first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>The LLRF upgrade modernizes the controls infrastructure from legacy VXI/PLC-5/SLC-500 to:</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Dimtel LLRF9 digital controllers (4 units, already procured)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Allen-Bradley CompactLogix/ControlLogix PLCs</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - EPICS-based supervisory control software</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Four-layer hardware protection architecture</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t>The SSA upgrade builds upon this modernized controls platform.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>3. SSA PROJECT SCOPE (INCLUDED)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>3a. SSA RF Source (WBS 1.0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Procurement of 16 x 65 kW SSA modules + 2 hot-swap spares from R&amp;K Company</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Design study, acceptance test protocol development, vendor collaboration</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - SSA test stand setup and commissioning at Building 122</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>3b. RF Distribution &amp; Combining (WBS 2.0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 4 x 4:1 coaxial combiners (6-1/8" inputs to WR2100 output)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 4 independent WR2100 waveguide runs from SSA building to cavities</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 4 high-power circulators (250+ kW CW @ 476 MHz)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - RF loads, directional couplers, transitions, waveguide supports</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="22" t="inlineStr">
+        <is>
+          <t>3c. Control Electronics &amp; Protection Systems (WBS 3.0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - LLRF9 reconfiguration for SSA vector sum control (hardware from LLRF upgrade)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - NEW Interface Chassis design for SSA interlock topology</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - RF MPS upgrade for 16-module fault detection and N-1 graceful degradation</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Arc detection system (Microstep-MIS sensors, carried over from LLRF upgrade design)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Waveform buffer system (reuse from LLRF upgrade, minimal reconfiguration)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - SSA module status monitoring (new: 16-channel VSWR/power/temperature)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Tuner motor controllers (carried over from LLRF upgrade, cavity-side)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - PPS REDESIGN for SSA (new safety chain without HVPS contactor/grounding switch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - NEW: NIP system (Non-Ionizing Protection) per SLAC ESH Chapter 50</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="22" t="inlineStr">
+        <is>
+          <t>3d. Software &amp; Integration (WBS 4.0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - EPICS IOC development for SSA modules, NIP, PPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - State machine / EPICS Coordinator extension for SSA operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Operator interface panels (EDM/CSS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Commissioning tools and scripts</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Documentation and operator training</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="22" t="inlineStr">
+        <is>
+          <t>3e. Installation &amp; Commissioning (WBS 5.0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - SSA module installation (4 stations, 4 modules each)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - RF distribution installation (waveguide, combiners, circulators)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Controls and cabling installation</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - System integration testing</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Phased commissioning (per-station turn-on)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="22" t="inlineStr">
+        <is>
+          <t>3f. Site Preparation &amp; Removal (WBS 6.0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Existing klystron and waveguide removal</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Cable tray relocation for new waveguide routing</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Equipment relocation (transformers, panels, cabinets)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="22" t="inlineStr">
+        <is>
+          <t>3g. Project Management (WBS 7.0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Technical program management (~0.5 FTE/yr over ~5-year project)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Safety reviews and PPS/NIP coordination with SLAC AD Safety Division</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="17" t="inlineStr">
+        <is>
+          <t>4. NOT INCLUDED IN SSA PROJECT SCOPE (reference items or other groups)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="22" t="inlineStr">
+        <is>
+          <t>4a. Infrastructure (WBS 8.0 - F&amp;O / Facilities scope)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 480 VAC distribution system (Substation 507 upgrade, 2.5-3 MVA transformer)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Cooling water upgrade (400 GPM LCW for SSA stations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Building extension and mezzanine (~636 + 300 sqft, two-story)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  These are carried as REFERENCE items for total project budgeting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="22" t="inlineStr">
+        <is>
+          <t>4b. LLRF Upgrade (separate project, prerequisite)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - LLRF9 controller procurement and installation</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - HVPS controller modernization (CompactLogix)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Original Interface Chassis design for klystron topology</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Legacy software migration (SNL -&gt; Python/EPICS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Klystron heater controller upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="22" t="inlineStr">
+        <is>
+          <t>4c. Items eliminated by SSA upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - HVPS (High Voltage Power Supply) - SSAs use internal 480V supplies</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Klystron - replaced by SSA modules</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Klystron cathode heater - not applicable to SSAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Drive amplifier - SSAs are self-contained</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="17" t="inlineStr">
+        <is>
+          <t>5. KEY TECHNICAL PARAMETERS</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Operating frequency: 476.3 MHz</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Total RF power: 16 x 65 kW = 1,040 kW</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - RF cavities: 4 (SPEAR3 storage ring)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - SSA per cavity: 4 modules combined via 4:1 coaxial combiner</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Waveguide: WR2100 (lambda_g = 80.4 cm at 476.3 MHz)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Cooling: LCW, 400 GPM total (~100 GPM/station, deltaT ~10K)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - SSA building: two-story, ~936 sqft total, 27 ft height, 9 ft clear under platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="17" t="inlineStr">
+        <is>
+          <t>6. PROJECT TIMELINE (ESTIMATED)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Overall: ~6-7 years, completion ~2032-2033</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Strongly dependent on Substation 507 upgrade schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Test stand procurement can begin near-term</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Facility design/construction constrained by engineering resources</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Integration testing limited to SPEAR summer shutdown windows (6-8 weeks)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -522,8 +1160,7 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -536,118 +1173,95 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Design Maturity: 5-15%  |  Labor Rate: $200/hr burdened  |  1 FTE = 1,740 hrs/yr  |  All costs in k$  |  Base year: 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+          <t>Design Maturity: 5-15% | Labor: $200/hr burdened | 1 FTE=1,740 hrs/yr | All costs in k$ | Base year: 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>NOTE: This estimate covers SSA upgrade scope ONLY. LLRF upgrade (klystron/HVPS controls modernization) is a prerequisite project funded separately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>WBS</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>M&amp;S (k$)</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>Labor (FTE)</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>Labor (k$)</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>Total (k$)</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G5" s="9" t="inlineStr">
         <is>
           <t>Conf.</t>
         </is>
       </c>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="H5" s="9" t="inlineStr">
         <is>
           <t>Basis of Estimate / Notes</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>SSA RF SOURCE</t>
         </is>
       </c>
-      <c r="C6" s="10" t="n"/>
-      <c r="D6" s="10" t="n"/>
-      <c r="E6" s="10" t="n"/>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
-      <c r="H6" s="10" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>SSA Modules (16 x 65 kW, R&amp;K Company)</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="n">
-        <v>4985.6</v>
-      </c>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="11" t="n">
-        <v>4985.6</v>
-      </c>
-      <c r="G7" s="11" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="H7" s="11" t="inlineStr">
-        <is>
-          <t>R&amp;K quote July 2025: $311,600/unit x 16 = $4,985,600. 476.3 MHz CW. Includes internal PS, LCW cooling, VSWR protection, Ethernet/serial control.</t>
-        </is>
-      </c>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="10" t="n"/>
+      <c r="G7" s="10" t="n"/>
+      <c r="H7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>SSA Spare Modules (2 units)</t>
+          <t>SSA Modules (16 x 65 kW, R&amp;K Company)</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>623.2</v>
+        <v>4985.6</v>
       </c>
       <c r="D8" s="11" t="n"/>
       <c r="E8" s="11" t="n"/>
       <c r="F8" s="11" t="n">
-        <v>623.2</v>
+        <v>4985.6</v>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
@@ -656,173 +1270,169 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>2 hot-swap spares @ $311,600 each. Industry practice for 16-module system. Enables rapid module replacement without waiting for vendor lead time.</t>
+          <t>R&amp;K quote July 2025: $311,600/unit x 16. 476.3 MHz CW. Includes internal 480V PS, LCW cooling, VSWR protection, Ethernet/serial control. See 'Reference Pricing' tab.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>SSA Design Study &amp; Prototype Test</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>348</v>
-      </c>
+          <t>SSA Spare Modules (2 hot-swap)</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>623.2</v>
+      </c>
+      <c r="D9" s="11" t="n"/>
+      <c r="E9" s="11" t="n"/>
       <c r="F9" s="11" t="n">
-        <v>348</v>
+        <v>623.2</v>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>H</t>
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>0.5 FTE prototype design + 0.5 FTE vendor collaboration and test iteration. Includes acceptance test protocol development. Per cover page row 7.</t>
+          <t>2 spares @ $311,600 each. Industry practice for 16-module system. Enables rapid replacement without vendor lead time.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>SSA Design Study &amp; Prototype Test</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="n"/>
+      <c r="D10" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="11" t="n">
+        <v>348</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>348</v>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>0.5 FTE prototype design/acceptance protocol + 0.5 FTE vendor collaboration &amp; test iteration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>SSA Test Stand (Bldg 122)</t>
         </is>
       </c>
-      <c r="C10" s="11" t="n">
+      <c r="C11" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D11" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E11" s="11" t="n">
         <v>174</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F11" s="11" t="n">
         <v>249</v>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
-        <is>
-          <t>High-power RF load (50 kW CW), power measurement, 480V service, LCW (~15 GPM per 3/10 mtg). Existing Bldg 122 LCW connection usable. 0.5 FTE setup/integration.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr"/>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>RF load (50 kW CW), power measurement, 480V service, LCW (~15 GPM). Existing Bldg 122 LCW connection usable (per 3/10 mtg).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr"/>
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>Subtotal WBS 1.0</t>
         </is>
       </c>
-      <c r="C11" s="12">
-        <f>SUM(C7:C10)</f>
-        <v/>
-      </c>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12">
-        <f>SUM(E7:E10)</f>
-        <v/>
-      </c>
-      <c r="F11" s="12">
-        <f>SUM(F7:F10)</f>
-        <v/>
-      </c>
-      <c r="G11" s="12" t="n"/>
-      <c r="H11" s="12" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="C12" s="12">
+        <f>SUM(C8:C11)</f>
+        <v/>
+      </c>
+      <c r="D12" s="12" t="n"/>
+      <c r="E12" s="12">
+        <f>SUM(E8:E11)</f>
+        <v/>
+      </c>
+      <c r="F12" s="12">
+        <f>SUM(F8:F11)</f>
+        <v/>
+      </c>
+      <c r="G12" s="12" t="n"/>
+      <c r="H12" s="12" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>RF DISTRIBUTION &amp; COMBINING</t>
         </is>
       </c>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
-      <c r="F13" s="10" t="n"/>
-      <c r="G13" s="10" t="n"/>
-      <c r="H13" s="10" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>6-1/8" Coaxial Combiners (4 x 4:1)</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="n">
-        <v>160</v>
-      </c>
-      <c r="D14" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E14" s="11" t="n">
-        <v>87</v>
-      </c>
-      <c r="F14" s="11" t="n">
-        <v>247</v>
-      </c>
-      <c r="G14" s="11" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H14" s="11" t="inlineStr">
-        <is>
-          <t>4 combiners, each combining 4 SSA outputs (6-1/8" coax) into single WR2100 port. ~$40k each installed. Each SSA cabinet outputs 6-1/8" coax per 3/10 mtg notes.</t>
-        </is>
-      </c>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="10" t="n"/>
+      <c r="H14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>WR2100 Waveguide Runs (4 independent)</t>
+          <t>6-1/8" Coaxial Combiners (4 x 4:1)</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>300</v>
+        <v>160</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>174</v>
+        <v>87</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>474</v>
+        <v>247</v>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
@@ -831,92 +1441,96 @@
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>4 independent WR2100 runs from SSA bldg to 4 cavities. Straight sections, H/E-plane bends, flex sections. ~10 lb/ft, Unistrut hangers every 8 ft. Lambda_g=80.4 cm at 476.3 MHz; lengths matched to +/- n*lambda_g.</t>
+          <t>4 combiners, each combining 4 SSA outputs (6-1/8" coax) into WR2100. ~$40k each. See Ref Pricing tab for vendor links.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Circulators (4 x 250+ kW @ 476 MHz)</t>
+          <t>WR2100 Waveguide Runs (4 independent)</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>0.15</v>
+        <v>0.5</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>52.2</v>
+        <v>174</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>452.2</v>
+        <v>474</v>
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>4 ferrite circulators, one per combined output. $80-120k each NEW. NOTE: PEP-II 1.5 MW circulators available (per 2/24 mtg) - if reusable, M&amp;S drops to ~$0. Carry new-buy as baseline.</t>
+          <t>4 runs from SSA bldg to 4 cavities. Straights, bends, flex sections. ~10 lb/ft, hangers every 8 ft. Lambda_g=80.4 cm. Mega Industries/Space Machine vendors.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>RF Loads (circulator loads, terminations)</t>
+          <t>Circulators (4 x 250+ kW @ 476 MHz)</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>80</v>
-      </c>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="11" t="n"/>
+        <v>400</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>52.2</v>
+      </c>
       <c r="F17" s="11" t="n">
-        <v>80</v>
+        <v>452.2</v>
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>4 circulator loads (water-cooled, ~250 kW each), waveguide terminations, dummy loads for commissioning. Loads cooled by HCW (separate from LCW per 3/10 mtg).</t>
+          <t>4 ferrite circulators. $80-120k each NEW (AFT Microwave, Mega Industries). PEP-II 1.5 MW units available (per 2/24 mtg) - if reusable, saves ~$400k.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Directional Couplers &amp; Transitions</t>
+          <t>RF Loads (circulator loads, terminations)</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D18" s="11" t="n"/>
       <c r="E18" s="11" t="n"/>
       <c r="F18" s="11" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -925,141 +1539,137 @@
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>Directional couplers at each combined output (4) and at each SSA output (16 may be internal). WR2100-to-coax transitions. Phase trimmers for combining efficiency.</t>
+          <t>4 water-cooled circulator loads (~250 kW each), waveguide terminations. HCW-cooled (separate from SSA LCW per 3/10 mtg).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Directional Couplers &amp; Transitions</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="D19" s="11" t="n"/>
+      <c r="E19" s="11" t="n"/>
+      <c r="F19" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>Directional couplers at combined outputs (4), WR2100-to-coax transitions, phase trimmers for combining efficiency. See Ref Pricing tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>Waveguide Supports, Hangers, Hardware</t>
         </is>
       </c>
-      <c r="C19" s="11" t="n">
+      <c r="C20" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="D19" s="11" t="n">
+      <c r="D20" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E20" s="11" t="n">
         <v>87</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F20" s="11" t="n">
         <v>137</v>
       </c>
-      <c r="G19" s="11" t="inlineStr">
+      <c r="G20" s="11" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H19" s="11" t="inlineStr">
-        <is>
-          <t>Unistrut channel, beam clamps, waveguide hangers every 8 ft, mounting hardware. Some supports from equipment platform structure above (per 3/10 mtg).</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr"/>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>Unistrut, beam clamps, hangers every 8 ft. Some supports from platform structure above (per 3/10 mtg).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr"/>
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>Subtotal WBS 2.0</t>
         </is>
       </c>
-      <c r="C20" s="12">
-        <f>SUM(C14:C19)</f>
-        <v/>
-      </c>
-      <c r="D20" s="12" t="n"/>
-      <c r="E20" s="12">
-        <f>SUM(E14:E19)</f>
-        <v/>
-      </c>
-      <c r="F20" s="12">
-        <f>SUM(F14:F19)</f>
-        <v/>
-      </c>
-      <c r="G20" s="12" t="n"/>
-      <c r="H20" s="12" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="C21" s="12">
+        <f>SUM(C15:C20)</f>
+        <v/>
+      </c>
+      <c r="D21" s="12" t="n"/>
+      <c r="E21" s="12">
+        <f>SUM(E15:E20)</f>
+        <v/>
+      </c>
+      <c r="F21" s="12">
+        <f>SUM(F15:F20)</f>
+        <v/>
+      </c>
+      <c r="G21" s="12" t="n"/>
+      <c r="H21" s="12" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>CONTROL ELECTRONICS</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="n"/>
-      <c r="D22" s="10" t="n"/>
-      <c r="E22" s="10" t="n"/>
-      <c r="F22" s="10" t="n"/>
-      <c r="G22" s="10" t="n"/>
-      <c r="H22" s="10" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>LLRF9 Controllers (4 x Dimtel LLRF9/500)</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="n">
-        <v>398</v>
-      </c>
-      <c r="D23" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E23" s="11" t="n">
-        <v>174</v>
-      </c>
-      <c r="F23" s="11" t="n">
-        <v>572</v>
-      </c>
-      <c r="G23" s="11" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="H23" s="11" t="inlineStr">
-        <is>
-          <t>Dimtel LLRF9/500 list $117k; 15% vol discount = $99.45k each x 4 = $397.8k. Each unit: 9 RF channels, FPGA interlocks &lt;1us, built-in EPICS IOC, 10 Hz scalar readback. 0.5 FTE for integration/configuration. Per LLRFUpgradeTaskListRev3.</t>
-        </is>
-      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>CONTROL ELECTRONICS &amp; PROTECTION SYSTEMS</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
+      <c r="F23" s="10" t="n"/>
+      <c r="G23" s="10" t="n"/>
+      <c r="H23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Interface Chassis (SSA topology)</t>
+          <t>LLRF9 SSA Reconfiguration (4 units)</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>261</v>
+        <v>174</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>286</v>
+        <v>194</v>
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
@@ -1068,168 +1678,168 @@
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>Central interlock hub: AND-logic, first-fault latching, fiber-optic HVPS ctrl, &lt;1us response. SSA version needs per-station permit logic + module-level status. PCB design + fabrication + chassis. CRITICAL PATH per 0_SYSTEM_DESIGN_REPORT.md Sec 8.3.</t>
+          <t>LLRF9 hardware installed during LLRF upgrade (no new purchase). SSA reconfiguration: new vector sum for 4-module combining, interlock remapping, firmware update. $20k for Dimtel support/firmware license. 0.5 FTE integration labor.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>RF MPS PLC (ControlLogix 1756)</t>
+          <t>Interface Chassis (NEW for SSA topology)</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
         <v>30</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>174</v>
+        <v>348</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>204</v>
+        <v>378</v>
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>M</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>AB ControlLogix PLC: $22k/set (detailed BOM in TaskListRev3: 5069-L320ER $3.7k, OF8 $1.5k x3, OX41 $451 x10, etc). SSA needs expanded I/O for 16 modules. +$8k for additional I/O modules. 0.5 FTE PLC programming + EPICS IOC.</t>
+          <t>New design required: SSA topology fundamentally different from klystron. Per-station permit logic, 16-module status aggregation, SSA-specific interlock sequencing. PCB design + fab + chassis. CRITICAL PATH.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Arc Detection System</t>
+          <t>RF MPS Upgrade (SSA topology)</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>0.3</v>
+        <v>0.75</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>104.4</v>
+        <v>261</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>124.4</v>
+        <v>296</v>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>M</t>
         </is>
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>Microstep-MIS sensors 470EUR x10=$5.1k, receivers 635EUR x6=$4.1k, cables=$1.1k, DB25=$200, mech adapters=$7k. Per TaskListRev3 quote from Erik Bystricky Nov 2024. 10 sensors (8 cavity + 1 kly + 1 circ), 5+1 receivers. Arc Detection Chassis: OR-gate + 10-bit latch.</t>
+          <t>Upgrade ControlLogix MPS for 16-module fault detection: individual module trip/bypass, graceful degradation (N-1 operation), new I/O cards for expanded inputs. AB PLC ~$22k + $13k additional I/O modules.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>Waveform Buffer System</t>
+          <t>Arc Detection System (carried over)</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>174</v>
+        <v>104.4</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>189</v>
+        <v>124.4</v>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>H</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Custom chassis: 8 RF + 4 HVPS channels, circular buffers, analog comparator trips, enhanced collector power protection algorithm. MCL ZX47-40LN-S+ detectors ($1.7k) + signal conditioning opamps + ADCs + chassis. Per WaveformBuffersforLLRFUpgrade.docx (Sebek, Jan 2026).</t>
+          <t>Microstep-MIS: sensors 470EUR x10, receivers 635EUR x6, cables, adapters. Same scope as LLRF upgrade. Per TaskListRev3 quote (Erik Bystricky Nov 2024). No change for SSA.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>SSA Module Status Monitoring</t>
+          <t>Waveform Buffer System (reuse from LLRF)</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>87</v>
+        <v>52.2</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>102</v>
+        <v>57.2</v>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>H</t>
         </is>
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>Per-module monitoring: VSWR, output power, temperature, fault status x16 modules. Ethernet/serial polling + analog readback. May be integrated into MPS PLC I/O or dedicated monitoring chassis.</t>
+          <t>Reuse waveform buffer installed during LLRF upgrade. Minimal SSA adaptation: reconfigure channel assignments for SSA monitoring points. $5k for any additional detectors/cables.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Tuner Motor Controllers (4 x Galil DMC-4143)</t>
+          <t>SSA Module Status Monitoring</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>104.4</v>
+        <v>87</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>114.4</v>
+        <v>102</v>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
@@ -1238,32 +1848,32 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Galil DMC-4143 4-axis controller $1,675 each x2 (1 operational + 1 spare). Motor drivers, cables, encoder interfaces. EPICS motor record support. Per galil/ commissioning docs. RISK: reliability TBD - test on booster tuners first (Sec 10.6).</t>
+          <t>Per-module monitoring: VSWR, output power, temperature, fault status x16 modules. Ethernet/serial polling + analog readback. New for SSA.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>PPS Interface Box</t>
+          <t>Tuner Motor Controllers (carried over)</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
         <v>5</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>69.59999999999999</v>
+        <v>34.8</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>74.59999999999999</v>
+        <v>39.8</v>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
@@ -1272,167 +1882,171 @@
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>Small Bud enclosure ~6x5x4in, 4 relays, status LEDs, inhibit buttons. Proven design per Ben Morris 3/5/2026 (pps_Ben.md). Identical to gallery/6575 modulator systems. Requires PPS group review and RSWCF. $2-5k materials.</t>
+          <t>Galil DMC-4143 controllers installed during LLRF upgrade. Cavity-side hardware, independent of RF source type. Minimal reconfiguration for SSA. $5k for spare parts/cables.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>PPS Redesign for SSA</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>261</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>276</v>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>Redesign required: HVPS contactor/grounding switch eliminated. New SSA PPS chain: 16x 480V SSA power permits, building access interlocks, emergency stop integration. Requires SLAC AD Safety Division review, RSWCF, formal change control.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
           <t>3.9</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>NIP System (Non-Ionizing Protection)</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="D32" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E32" s="11" t="n">
+        <v>261</v>
+      </c>
+      <c r="F32" s="11" t="n">
+        <v>321</v>
+      </c>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H32" s="11" t="inlineStr">
+        <is>
+          <t>NEW: Required per SLAC ESH Ch.50 for 1,040 kW RF in new SSA building. RF field monitors/sensors ($15-25k), door interlocks ($10-15k), warning beacons/signage ($5k), interlock controller ($10-15k). 0.75 FTE: hazard analysis, RFSP development, safety review, documentation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>Cables, Connectors, Integration Materials</t>
         </is>
       </c>
-      <c r="C31" s="11" t="n">
-        <v>40</v>
-      </c>
-      <c r="D31" s="11" t="n"/>
-      <c r="E31" s="11" t="n"/>
-      <c r="F31" s="11" t="n">
-        <v>40</v>
-      </c>
-      <c r="G31" s="11" t="inlineStr">
+      <c r="C33" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="11" t="n"/>
+      <c r="F33" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H31" s="11" t="inlineStr">
-        <is>
-          <t>RF cables (SMA, Type-N), fiber optic links (HFBR-1412/2412), LEMO interlock cables, multi-conductor digital cables, power supplies, rack hardware, PDUs, labels. ~10% of WBS 3.1-3.8 hardware.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="12" t="inlineStr"/>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>RF cables (SMA, Type-N), fiber optic links, LEMO interlock cables, Ethernet, 480V power cables to SSAs, rack hardware, PDUs. Higher than LLRF upgrade due to 16 distributed modules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr"/>
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>Subtotal WBS 3.0</t>
         </is>
       </c>
-      <c r="C32" s="12">
-        <f>SUM(C23:C31)</f>
-        <v/>
-      </c>
-      <c r="D32" s="12" t="n"/>
-      <c r="E32" s="12">
-        <f>SUM(E23:E31)</f>
-        <v/>
-      </c>
-      <c r="F32" s="12">
-        <f>SUM(F23:F31)</f>
-        <v/>
-      </c>
-      <c r="G32" s="12" t="n"/>
-      <c r="H32" s="12" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="C34" s="12">
+        <f>SUM(C24:C33)</f>
+        <v/>
+      </c>
+      <c r="D34" s="12" t="n"/>
+      <c r="E34" s="12">
+        <f>SUM(E24:E33)</f>
+        <v/>
+      </c>
+      <c r="F34" s="12">
+        <f>SUM(F24:F33)</f>
+        <v/>
+      </c>
+      <c r="G34" s="12" t="n"/>
+      <c r="H34" s="12" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="B34" s="10" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>SOFTWARE &amp; INTEGRATION</t>
         </is>
       </c>
-      <c r="C34" s="10" t="n"/>
-      <c r="D34" s="10" t="n"/>
-      <c r="E34" s="10" t="n"/>
-      <c r="F34" s="10" t="n"/>
-      <c r="G34" s="10" t="n"/>
-      <c r="H34" s="10" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="11" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="B35" s="11" t="inlineStr">
-        <is>
-          <t>EPICS IOC Development</t>
-        </is>
-      </c>
-      <c r="C35" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="D35" s="11" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E35" s="11" t="n">
-        <v>261</v>
-      </c>
-      <c r="F35" s="11" t="n">
-        <v>271</v>
-      </c>
-      <c r="G35" s="11" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H35" s="11" t="inlineStr">
-        <is>
-          <t>IOCs for: LLRF9 (Dimtel provides baseline, SPEAR customization), MPS ControlLogix (EtherIP/pycomm3), SSA module monitoring (ASYN/StreamDevice), Waveform Buffer, Chroma heater ASYN driver. Dev tools + test licenses.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="11" t="inlineStr">
-        <is>
-          <t>4.2</t>
-        </is>
-      </c>
-      <c r="B36" s="11" t="inlineStr">
-        <is>
-          <t>State Machine / EPICS Coordinator</t>
-        </is>
-      </c>
-      <c r="C36" s="11" t="n"/>
-      <c r="D36" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" s="11" t="n">
-        <v>348</v>
-      </c>
-      <c r="F36" s="11" t="n">
-        <v>348</v>
-      </c>
-      <c r="G36" s="11" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H36" s="11" t="inlineStr">
-        <is>
-          <t>Python/MATLAB supervisory control ~1 Hz. States: OFF/PARK/TUNE/ON_CW. Fault handling, auto-recovery, HVPS ramp control, heater warm-up/cooldown sequences. Load angle offset loop (balance 4 cavity fields). CRITICAL: largest untouched software scope per Sec 19.3.</t>
-        </is>
-      </c>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="10" t="n"/>
+      <c r="G36" s="10" t="n"/>
+      <c r="H36" s="10" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>Operator Interface (EDM/CSS Panels)</t>
-        </is>
-      </c>
-      <c r="C37" s="11" t="n"/>
+          <t>EPICS IOC Development (SSA-specific)</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="n">
+        <v>10</v>
+      </c>
       <c r="D37" s="11" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>87</v>
+        <v>261</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>87</v>
+        <v>271</v>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
@@ -1441,32 +2055,30 @@
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>EDM/CSS operator displays: station overview, per-module SSA status, LLRF9 summary, MPS fault tree, waveform displays, tuner positions, HVPS status. Based on existing rf_station_4CVSPR.edl pattern.</t>
+          <t>SSA module IOCs (ASYN/StreamDevice for R&amp;K Ethernet/serial), NIP system IOC, PPS status IOC. LLRF9 IOC carries over from LLRF upgrade. SSA-specific customization.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>Commissioning Tools &amp; Scripts</t>
-        </is>
-      </c>
-      <c r="C38" s="11" t="n">
-        <v>5</v>
-      </c>
+          <t>State Machine / EPICS Coordinator (SSA)</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>87</v>
+        <v>348</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>92</v>
+        <v>348</v>
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
@@ -1475,19 +2087,19 @@
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>MATLAB/Python tools for: SSA phase calibration, combiner efficiency optimization, interlock chain verification, automated fault injection testing, performance logging. Per legacy rf_calib.st (2,800+ lines).</t>
+          <t>Extend LLRF coordinator for SSA: module startup/shutdown sequencing, hot-swap logic, graceful degradation (N-1 mode), per-station state machine. CRITICAL: largest untouched software scope.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>Documentation &amp; Training</t>
+          <t>Operator Interface (EDM/CSS Panels)</t>
         </is>
       </c>
       <c r="C39" s="11" t="n"/>
@@ -1507,141 +2119,139 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>System documentation, as-built drawings, operator training materials, maintenance procedures. ~25 schematics for MPS + ~25 for HVPS (per TaskListRev3). Training for operations staff on new SSA system.</t>
+          <t>New displays: per-module SSA status, combining efficiency, NIP status, 16-channel fault tree. Extend existing panels from LLRF upgrade.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="12" t="inlineStr"/>
-      <c r="B40" s="12" t="inlineStr">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>Commissioning Tools &amp; Scripts</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D40" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E40" s="11" t="n">
+        <v>87</v>
+      </c>
+      <c r="F40" s="11" t="n">
+        <v>92</v>
+      </c>
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>SSA phase calibration, combiner efficiency optimization, module acceptance test scripts, fault injection testing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>Documentation &amp; Training</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="n"/>
+      <c r="D41" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E41" s="11" t="n">
+        <v>87</v>
+      </c>
+      <c r="F41" s="11" t="n">
+        <v>87</v>
+      </c>
+      <c r="G41" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H41" s="11" t="inlineStr">
+        <is>
+          <t>SSA system docs, NIP RFSP documentation, as-builts, operator training on SSA operations &amp; module replacement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr"/>
+      <c r="B42" s="12" t="inlineStr">
         <is>
           <t>Subtotal WBS 4.0</t>
         </is>
       </c>
-      <c r="C40" s="12">
-        <f>SUM(C35:C39)</f>
-        <v/>
-      </c>
-      <c r="D40" s="12" t="n"/>
-      <c r="E40" s="12">
-        <f>SUM(E35:E39)</f>
-        <v/>
-      </c>
-      <c r="F40" s="12">
-        <f>SUM(F35:F39)</f>
-        <v/>
-      </c>
-      <c r="G40" s="12" t="n"/>
-      <c r="H40" s="12" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="C42" s="12">
+        <f>SUM(C37:C41)</f>
+        <v/>
+      </c>
+      <c r="D42" s="12" t="n"/>
+      <c r="E42" s="12">
+        <f>SUM(E37:E41)</f>
+        <v/>
+      </c>
+      <c r="F42" s="12">
+        <f>SUM(F37:F41)</f>
+        <v/>
+      </c>
+      <c r="G42" s="12" t="n"/>
+      <c r="H42" s="12" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="B42" s="10" t="inlineStr">
+      <c r="B44" s="10" t="inlineStr">
         <is>
           <t>INSTALLATION &amp; COMMISSIONING</t>
         </is>
       </c>
-      <c r="C42" s="10" t="n"/>
-      <c r="D42" s="10" t="n"/>
-      <c r="E42" s="10" t="n"/>
-      <c r="F42" s="10" t="n"/>
-      <c r="G42" s="10" t="n"/>
-      <c r="H42" s="10" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="11" t="inlineStr">
-        <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="B43" s="11" t="inlineStr">
-        <is>
-          <t>SSA Module Installation (4 stations)</t>
-        </is>
-      </c>
-      <c r="C43" s="11" t="n">
-        <v>50</v>
-      </c>
-      <c r="D43" s="11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E43" s="11" t="n">
-        <v>480</v>
-      </c>
-      <c r="F43" s="11" t="n">
-        <v>530</v>
-      </c>
-      <c r="G43" s="11" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H43" s="11" t="inlineStr">
-        <is>
-          <t>4 person-3 weeks/station x 4 stations = 12 person-months. Rack mounting, 480V power connections, LCW plumbing to each module, RF output cabling, control/interlock wiring. $50k for tools, rigging, consumables. Per cover page row 8.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="11" t="inlineStr">
-        <is>
-          <t>5.2</t>
-        </is>
-      </c>
-      <c r="B44" s="11" t="inlineStr">
-        <is>
-          <t>RF Distribution Installation</t>
-        </is>
-      </c>
-      <c r="C44" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="D44" s="11" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E44" s="11" t="n">
-        <v>261</v>
-      </c>
-      <c r="F44" s="11" t="n">
-        <v>291</v>
-      </c>
-      <c r="G44" s="11" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H44" s="11" t="inlineStr">
-        <is>
-          <t>Waveguide assembly, circulator installation (vertical orientation per 2/24 mtg), combiner hookup, load installation. Requires crane for heavy components. Waveguide alignment and RF leak testing.</t>
-        </is>
-      </c>
+      <c r="C44" s="10" t="n"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="10" t="n"/>
+      <c r="G44" s="10" t="n"/>
+      <c r="H44" s="10" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>Controls &amp; Cabling Installation</t>
+          <t>SSA Module Installation (4 stations)</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>0.5</v>
+        <v>1.38</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>174</v>
+        <v>480</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>194</v>
+        <v>530</v>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
@@ -1650,30 +2260,32 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>LLRF9 rack mounting, MPS PLC wiring, Interface Chassis installation, arc detector fiber routing, interlock cabling, Ethernet network, fiber-optic links to HVPS (HFBR-1412/2412).</t>
+          <t>4 person x 3 weeks/station x 4 stations. Rack mounting, 480V power, LCW plumbing, RF cabling, control/interlock wiring. Per cover page row 8.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>System Integration Testing</t>
-        </is>
-      </c>
-      <c r="C46" s="11" t="n"/>
+          <t>RF Distribution Installation</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="n">
+        <v>30</v>
+      </c>
       <c r="D46" s="11" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>174</v>
+        <v>261</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>174</v>
+        <v>291</v>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
@@ -1682,418 +2294,416 @@
       </c>
       <c r="H46" s="11" t="inlineStr">
         <is>
-          <t>End-to-end interlock chain testing (Layer 1-4), EPICS PV verification, fault injection testing, waveform capture validation. Limited window due to SPEAR operations (per Sec 19.1 constraint).</t>
+          <t>Waveguide assembly, circulator installation (vertical per 2/24 mtg), combiner hookup, load installation. Crane required for heavy components.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>Phased Commissioning (per-station turn-on)</t>
+          <t>Controls &amp; Cabling Installation</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
         <v>20</v>
       </c>
       <c r="D47" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E47" s="11" t="n">
+        <v>174</v>
+      </c>
+      <c r="F47" s="11" t="n">
+        <v>194</v>
+      </c>
+      <c r="G47" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H47" s="11" t="inlineStr">
+        <is>
+          <t>MPS rewiring, Interface Chassis install, NIP sensor installation, interlock cabling, Ethernet network for 16 SSA modules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t>System Integration Testing</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="n"/>
+      <c r="D48" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E48" s="11" t="n">
+        <v>174</v>
+      </c>
+      <c r="F48" s="11" t="n">
+        <v>174</v>
+      </c>
+      <c r="G48" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H48" s="11" t="inlineStr">
+        <is>
+          <t>End-to-end interlock testing, NIP verification, EPICS PV verification, fault injection. Limited window due to SPEAR operations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t>Phased Commissioning (per-station)</t>
+        </is>
+      </c>
+      <c r="C49" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D49" s="11" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="E47" s="11" t="n">
+      <c r="E49" s="11" t="n">
         <v>240</v>
       </c>
-      <c r="F47" s="11" t="n">
+      <c r="F49" s="11" t="n">
         <v>260</v>
       </c>
-      <c r="G47" s="11" t="inlineStr">
+      <c r="G49" s="11" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H47" s="11" t="inlineStr">
-        <is>
-          <t>6 person-2 months commissioning (per cover page row 8). Incremental power ramp per station. Performance validation: amplitude stability &lt;0.1%, phase &lt;0.1 deg. Includes Dimtel 1-week on-site support per LLRF9.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="12" t="inlineStr"/>
-      <c r="B48" s="12" t="inlineStr">
+      <c r="H49" s="11" t="inlineStr">
+        <is>
+          <t>6 person x 2 months commissioning. Incremental per-station power ramp. Performance: amplitude &lt;0.1%, phase &lt;0.1 deg.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr"/>
+      <c r="B50" s="12" t="inlineStr">
         <is>
           <t>Subtotal WBS 5.0</t>
         </is>
       </c>
-      <c r="C48" s="12">
-        <f>SUM(C43:C47)</f>
-        <v/>
-      </c>
-      <c r="D48" s="12" t="n"/>
-      <c r="E48" s="12">
-        <f>SUM(E43:E47)</f>
-        <v/>
-      </c>
-      <c r="F48" s="12">
-        <f>SUM(F43:F47)</f>
-        <v/>
-      </c>
-      <c r="G48" s="12" t="n"/>
-      <c r="H48" s="12" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="10" t="inlineStr">
+      <c r="C50" s="12">
+        <f>SUM(C45:C49)</f>
+        <v/>
+      </c>
+      <c r="D50" s="12" t="n"/>
+      <c r="E50" s="12">
+        <f>SUM(E45:E49)</f>
+        <v/>
+      </c>
+      <c r="F50" s="12">
+        <f>SUM(F45:F49)</f>
+        <v/>
+      </c>
+      <c r="G50" s="12" t="n"/>
+      <c r="H50" s="12" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="B50" s="10" t="inlineStr">
+      <c r="B52" s="10" t="inlineStr">
         <is>
           <t>SITE PREPARATION &amp; REMOVAL</t>
         </is>
       </c>
-      <c r="C50" s="10" t="n"/>
-      <c r="D50" s="10" t="n"/>
-      <c r="E50" s="10" t="n"/>
-      <c r="F50" s="10" t="n"/>
-      <c r="G50" s="10" t="n"/>
-      <c r="H50" s="10" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="11" t="inlineStr">
-        <is>
-          <t>6.1</t>
-        </is>
-      </c>
-      <c r="B51" s="11" t="inlineStr">
-        <is>
-          <t>Existing Waveguide Removal</t>
-        </is>
-      </c>
-      <c r="C51" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D51" s="11" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E51" s="11" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="F51" s="11" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="G51" s="11" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="H51" s="11" t="inlineStr">
-        <is>
-          <t>Remove existing klystron waveguide (magic tee splitters, existing WR2100 run). Roof waveguide splitters removed; direct 1:1 SSA-to-cavity runs replace them (per 2/24 mtg).</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="11" t="inlineStr">
-        <is>
-          <t>6.2</t>
-        </is>
-      </c>
-      <c r="B52" s="11" t="inlineStr">
-        <is>
-          <t>Cable Tray Relocation</t>
-        </is>
-      </c>
-      <c r="C52" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="D52" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E52" s="11" t="n">
-        <v>87</v>
-      </c>
-      <c r="F52" s="11" t="n">
-        <v>97</v>
-      </c>
-      <c r="G52" s="11" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H52" s="11" t="inlineStr">
-        <is>
-          <t>Straighten S-shaped cable trays for 4 waveguide runs on roof (per 2/24 mtg). Relocate cable trays between 118 and ring ~10 ft outward for clearance. 4 person-1 month per cover page row 9.</t>
-        </is>
-      </c>
+      <c r="C52" s="10" t="n"/>
+      <c r="D52" s="10" t="n"/>
+      <c r="E52" s="10" t="n"/>
+      <c r="F52" s="10" t="n"/>
+      <c r="G52" s="10" t="n"/>
+      <c r="H52" s="10" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t>Existing Klystron/Waveguide Removal</t>
+        </is>
+      </c>
+      <c r="C53" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D53" s="11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E53" s="11" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="F53" s="11" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="G53" s="11" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="H53" s="11" t="inlineStr">
+        <is>
+          <t>Remove klystron, existing waveguide, magic tee splitters. Roof splitters removed; replaced by direct SSA-to-cavity runs (per 2/24 mtg).</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>Cable Tray Relocation</t>
+        </is>
+      </c>
+      <c r="C54" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D54" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E54" s="11" t="n">
+        <v>87</v>
+      </c>
+      <c r="F54" s="11" t="n">
+        <v>97</v>
+      </c>
+      <c r="G54" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H54" s="11" t="inlineStr">
+        <is>
+          <t>Straighten S-shaped cable trays on roof (per 2/24 mtg). Relocate trays between 118 and ring ~10 ft outward.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
           <t>6.3</t>
         </is>
       </c>
-      <c r="B53" s="11" t="inlineStr">
+      <c r="B55" s="11" t="inlineStr">
         <is>
           <t>Equipment Relocation</t>
         </is>
       </c>
-      <c r="C53" s="11" t="n">
+      <c r="C55" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="D53" s="11" t="n">
+      <c r="D55" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="E53" s="11" t="n">
+      <c r="E55" s="11" t="n">
         <v>87</v>
       </c>
-      <c r="F53" s="11" t="n">
+      <c r="F55" s="11" t="n">
         <v>102</v>
       </c>
-      <c r="G53" s="11" t="inlineStr">
+      <c r="G55" s="11" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H53" s="11" t="inlineStr">
-        <is>
-          <t>Relocate transformers (2-3), distribution panels, MPS controls cabinets during downtime. Remove old air-handler/chiller behind 507 (per 2/24 mtg). Relocate condensing unit 5-10 ft.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="12" t="inlineStr"/>
-      <c r="B54" s="12" t="inlineStr">
+      <c r="H55" s="11" t="inlineStr">
+        <is>
+          <t>Relocate transformers (2-3), panels, controls cabinets during downtime. Remove old air-handler/chiller behind 507 (per 2/24 mtg).</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="inlineStr"/>
+      <c r="B56" s="12" t="inlineStr">
         <is>
           <t>Subtotal WBS 6.0</t>
         </is>
       </c>
-      <c r="C54" s="12">
-        <f>SUM(C51:C53)</f>
-        <v/>
-      </c>
-      <c r="D54" s="12" t="n"/>
-      <c r="E54" s="12">
-        <f>SUM(E51:E53)</f>
-        <v/>
-      </c>
-      <c r="F54" s="12">
-        <f>SUM(F51:F53)</f>
-        <v/>
-      </c>
-      <c r="G54" s="12" t="n"/>
-      <c r="H54" s="12" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="10" t="inlineStr">
+      <c r="C56" s="12">
+        <f>SUM(C53:C55)</f>
+        <v/>
+      </c>
+      <c r="D56" s="12" t="n"/>
+      <c r="E56" s="12">
+        <f>SUM(E53:E55)</f>
+        <v/>
+      </c>
+      <c r="F56" s="12">
+        <f>SUM(F53:F55)</f>
+        <v/>
+      </c>
+      <c r="G56" s="12" t="n"/>
+      <c r="H56" s="12" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="B56" s="10" t="inlineStr">
+      <c r="B58" s="10" t="inlineStr">
         <is>
           <t>PROJECT MANAGEMENT</t>
         </is>
       </c>
-      <c r="C56" s="10" t="n"/>
-      <c r="D56" s="10" t="n"/>
-      <c r="E56" s="10" t="n"/>
-      <c r="F56" s="10" t="n"/>
-      <c r="G56" s="10" t="n"/>
-      <c r="H56" s="10" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="11" t="inlineStr">
+      <c r="C58" s="10" t="n"/>
+      <c r="D58" s="10" t="n"/>
+      <c r="E58" s="10" t="n"/>
+      <c r="F58" s="10" t="n"/>
+      <c r="G58" s="10" t="n"/>
+      <c r="H58" s="10" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="11" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="B57" s="11" t="inlineStr">
+      <c r="B59" s="11" t="inlineStr">
         <is>
           <t>Technical Program Management</t>
         </is>
       </c>
-      <c r="C57" s="11" t="n">
+      <c r="C59" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="D57" s="11" t="n">
+      <c r="D59" s="11" t="n">
         <v>2.5</v>
       </c>
-      <c r="E57" s="11" t="n">
+      <c r="E59" s="11" t="n">
         <v>870</v>
       </c>
-      <c r="F57" s="11" t="n">
+      <c r="F59" s="11" t="n">
         <v>890</v>
       </c>
-      <c r="G57" s="11" t="inlineStr">
+      <c r="G59" s="11" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H57" s="11" t="inlineStr">
-        <is>
-          <t>~0.5 FTE/yr average over ~5-year project. Schedule management, resource coordination, vendor management (R&amp;K, Dimtel), progress reporting. M&amp;S for travel to vendor sites, DOE reviews.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="11" t="inlineStr">
+      <c r="H59" s="11" t="inlineStr">
+        <is>
+          <t>~0.5 FTE/yr over ~5-year project. Schedule, resource, vendor management (R&amp;K, Dimtel). M&amp;S for travel, DOE reviews.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
         <is>
           <t>7.2</t>
         </is>
       </c>
-      <c r="B58" s="11" t="inlineStr">
-        <is>
-          <t>Safety Reviews &amp; PPS Coordination</t>
-        </is>
-      </c>
-      <c r="C58" s="11" t="n">
+      <c r="B60" s="11" t="inlineStr">
+        <is>
+          <t>Safety Reviews &amp; PPS/NIP Coordination</t>
+        </is>
+      </c>
+      <c r="C60" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="D58" s="11" t="n">
+      <c r="D60" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="E58" s="11" t="n">
+      <c r="E60" s="11" t="n">
         <v>174</v>
       </c>
-      <c r="F58" s="11" t="n">
+      <c r="F60" s="11" t="n">
         <v>184</v>
       </c>
-      <c r="G58" s="11" t="inlineStr">
+      <c r="G60" s="11" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H58" s="11" t="inlineStr">
-        <is>
-          <t>PPS review/approval with SLAC AD Safety Division. LOTO procedures, arc flash analysis, OSHA compliance for building/stairway. Formal change control documentation, RSWCF. Early engagement critical (Sec 9.4).</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr"/>
-      <c r="B59" s="12" t="inlineStr">
+      <c r="H60" s="11" t="inlineStr">
+        <is>
+          <t>PPS + NIP review/approval with SLAC AD Safety Division. LOTO, arc flash, OSHA compliance. RSWCF, RFSP documentation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="12" t="inlineStr"/>
+      <c r="B61" s="12" t="inlineStr">
         <is>
           <t>Subtotal WBS 7.0</t>
         </is>
       </c>
-      <c r="C59" s="12">
-        <f>SUM(C57:C58)</f>
-        <v/>
-      </c>
-      <c r="D59" s="12" t="n"/>
-      <c r="E59" s="12">
-        <f>SUM(E57:E58)</f>
-        <v/>
-      </c>
-      <c r="F59" s="12">
-        <f>SUM(F57:F58)</f>
-        <v/>
-      </c>
-      <c r="G59" s="12" t="n"/>
-      <c r="H59" s="12" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="10" t="inlineStr">
+      <c r="C61" s="12">
+        <f>SUM(C59:C60)</f>
+        <v/>
+      </c>
+      <c r="D61" s="12" t="n"/>
+      <c r="E61" s="12">
+        <f>SUM(E59:E60)</f>
+        <v/>
+      </c>
+      <c r="F61" s="12">
+        <f>SUM(F59:F60)</f>
+        <v/>
+      </c>
+      <c r="G61" s="12" t="n"/>
+      <c r="H61" s="12" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="B61" s="10" t="inlineStr">
-        <is>
-          <t>INFRASTRUCTURE (Reference - other groups may provide independent estimates)</t>
-        </is>
-      </c>
-      <c r="C61" s="10" t="n"/>
-      <c r="D61" s="10" t="n"/>
-      <c r="E61" s="10" t="n"/>
-      <c r="F61" s="10" t="n"/>
-      <c r="G61" s="10" t="n"/>
-      <c r="H61" s="10" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="13" t="inlineStr">
-        <is>
-          <t>8.1</t>
-        </is>
-      </c>
-      <c r="B62" s="13" t="inlineStr">
-        <is>
-          <t>480 VAC Distribution System</t>
-        </is>
-      </c>
-      <c r="C62" s="13" t="n">
-        <v>900</v>
-      </c>
-      <c r="D62" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E62" s="13" t="n">
-        <v>696</v>
-      </c>
-      <c r="F62" s="13" t="n">
-        <v>1596</v>
-      </c>
-      <c r="G62" s="13" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="H62" s="13" t="inlineStr">
-        <is>
-          <t>REFERENCE: Substation 507 option ($1-2M per 1/27 mtg). 2.5-3 MVA transformer 12kV-480V (~$150-200k); 12kV feed + switchgear (~$300k); 480V panels/breakers 4-8 buckets/SSA (~$200k); civil/cable (~$200k). F&amp;O/Andi scope. Alt: Sub 502 = $8-9M.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="13" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
-      </c>
-      <c r="B63" s="13" t="inlineStr">
-        <is>
-          <t>Cooling Water (LCW/HCW)</t>
-        </is>
-      </c>
-      <c r="C63" s="13" t="n">
-        <v>250</v>
-      </c>
-      <c r="D63" s="13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E63" s="13" t="n">
-        <v>522</v>
-      </c>
-      <c r="F63" s="13" t="n">
-        <v>772</v>
-      </c>
-      <c r="G63" s="13" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="H63" s="13" t="inlineStr">
-        <is>
-          <t>REFERENCE: 400 GPM LCW for 4 SSA stations. Option B: new 6"+ connection to main header (per 3/10 mtg). 4"-&gt;6"+ piping upgrade ($100-150k); manifolds/valves/controls ($50-75k); HCW for loads ($25-50k). Javier/F&amp;O scope. Summer shutdown required.</t>
-        </is>
-      </c>
+      <c r="B63" s="10" t="inlineStr">
+        <is>
+          <t>INFRASTRUCTURE (Reference - F&amp;O / other groups' scope)</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="n"/>
+      <c r="D63" s="10" t="n"/>
+      <c r="E63" s="10" t="n"/>
+      <c r="F63" s="10" t="n"/>
+      <c r="G63" s="10" t="n"/>
+      <c r="H63" s="10" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="B64" s="13" t="inlineStr">
         <is>
-          <t>Building Extension &amp; Mezzanine</t>
+          <t>480 VAC Distribution System</t>
         </is>
       </c>
       <c r="C64" s="13" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="D64" s="13" t="n">
         <v>2</v>
@@ -2102,273 +2712,372 @@
         <v>696</v>
       </c>
       <c r="F64" s="13" t="n">
+        <v>1596</v>
+      </c>
+      <c r="G64" s="13" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H64" s="13" t="inlineStr">
+        <is>
+          <t>REF: Sub 507 option ($1-2M per 1/27 mtg). 2.5-3 MVA transformer, 12kV feed, 480V panels for 16 SSAs. Alt: Sub 502 = $8-9M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="13" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="B65" s="13" t="inlineStr">
+        <is>
+          <t>Cooling Water (LCW/HCW)</t>
+        </is>
+      </c>
+      <c r="C65" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="D65" s="13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E65" s="13" t="n">
+        <v>522</v>
+      </c>
+      <c r="F65" s="13" t="n">
+        <v>772</v>
+      </c>
+      <c r="G65" s="13" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H65" s="13" t="inlineStr">
+        <is>
+          <t>REF: 400 GPM LCW for 4 SSA stations. Option B: new 6"+ connection (per 3/10 mtg). Summer shutdown required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="13" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="B66" s="13" t="inlineStr">
+        <is>
+          <t>Building Extension &amp; Mezzanine</t>
+        </is>
+      </c>
+      <c r="C66" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="D66" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E66" s="13" t="n">
+        <v>696</v>
+      </c>
+      <c r="F66" s="13" t="n">
         <v>1196</v>
       </c>
-      <c r="G64" s="13" t="inlineStr">
+      <c r="G66" s="13" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="H64" s="13" t="inlineStr">
-        <is>
-          <t>REFERENCE: ~636 sqft extension + ~300 sqft mezzanine @ 27 ft. Two-story layout (per 2/24 mtg). OSHA stairway (~25 risers). Roll-up doors. HVAC for SSA heat. Seismic. F&amp;O prior test facility estimate: $1.3M (per 1/27 mtg). Javier/F&amp;O scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="12" t="inlineStr"/>
-      <c r="B65" s="12" t="inlineStr">
+      <c r="H66" s="13" t="inlineStr">
+        <is>
+          <t>REF: ~636 sqft + ~300 sqft mezzanine @ 27 ft. Two-story layout (per 2/24 mtg). OSHA stairway. Roll-up doors. Seismic. F&amp;O prior estimate $1.3M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="12" t="inlineStr"/>
+      <c r="B67" s="12" t="inlineStr">
         <is>
           <t>Subtotal WBS 8.0 (Reference)</t>
         </is>
       </c>
-      <c r="C65" s="12">
-        <f>SUM(C62:C64)</f>
-        <v/>
-      </c>
-      <c r="D65" s="12" t="n"/>
-      <c r="E65" s="12">
-        <f>SUM(E62:E64)</f>
-        <v/>
-      </c>
-      <c r="F65" s="12">
-        <f>SUM(F62:F64)</f>
-        <v/>
-      </c>
-      <c r="G65" s="12" t="n"/>
-      <c r="H65" s="12" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="14" t="inlineStr"/>
-      <c r="B67" s="14" t="inlineStr">
+      <c r="C67" s="12">
+        <f>SUM(C64:C66)</f>
+        <v/>
+      </c>
+      <c r="D67" s="12" t="n"/>
+      <c r="E67" s="12">
+        <f>SUM(E64:E66)</f>
+        <v/>
+      </c>
+      <c r="F67" s="12">
+        <f>SUM(F64:F66)</f>
+        <v/>
+      </c>
+      <c r="G67" s="12" t="n"/>
+      <c r="H67" s="12" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="14" t="n"/>
+      <c r="B69" s="14" t="inlineStr">
         <is>
           <t>RF/CONTROLS SCOPE SUBTOTAL (WBS 1-7)</t>
         </is>
       </c>
-      <c r="C67" s="15">
-        <f>C11+C20+C32+C40+C48+C54+C59</f>
-        <v/>
-      </c>
-      <c r="D67" s="14" t="n"/>
-      <c r="E67" s="14">
-        <f>E11+E20+E32+E40+E48+E54+E59</f>
-        <v/>
-      </c>
-      <c r="F67" s="14">
-        <f>F11+F20+F32+F40+F48+F54+F59</f>
-        <v/>
-      </c>
-      <c r="G67" s="14" t="n"/>
-      <c r="H67" s="14" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="14" t="n"/>
-      <c r="B68" s="14" t="inlineStr">
+      <c r="C69" s="14">
+        <f>C12+C21+C34+C42+C50+C56+C61</f>
+        <v/>
+      </c>
+      <c r="D69" s="14" t="n"/>
+      <c r="E69" s="14">
+        <f>E12+E21+E34+E42+E50+E56+E61</f>
+        <v/>
+      </c>
+      <c r="F69" s="14">
+        <f>F12+F21+F34+F42+F50+F56+F61</f>
+        <v/>
+      </c>
+      <c r="G69" s="14" t="n"/>
+      <c r="H69" s="14" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="14" t="n"/>
+      <c r="B70" s="14" t="inlineStr">
         <is>
           <t>INFRASTRUCTURE REFERENCE (WBS 8)</t>
         </is>
       </c>
-      <c r="C68" s="14">
-        <f>C65</f>
-        <v/>
-      </c>
-      <c r="D68" s="14" t="n"/>
-      <c r="E68" s="14">
-        <f>E65</f>
-        <v/>
-      </c>
-      <c r="F68" s="14">
-        <f>F65</f>
-        <v/>
-      </c>
-      <c r="G68" s="14" t="n"/>
-      <c r="H68" s="14" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="16" t="n"/>
-      <c r="B69" s="16" t="inlineStr">
+      <c r="C70" s="14">
+        <f>C67</f>
+        <v/>
+      </c>
+      <c r="D70" s="14" t="n"/>
+      <c r="E70" s="14">
+        <f>E67</f>
+        <v/>
+      </c>
+      <c r="F70" s="14">
+        <f>F67</f>
+        <v/>
+      </c>
+      <c r="G70" s="14" t="n"/>
+      <c r="H70" s="14" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="16" t="n"/>
+      <c r="B71" s="16" t="inlineStr">
         <is>
           <t>PROJECT BASE ESTIMATE (WBS 1-8)</t>
         </is>
       </c>
-      <c r="C69" s="16">
-        <f>C67+C68</f>
-        <v/>
-      </c>
-      <c r="D69" s="16" t="n"/>
-      <c r="E69" s="16">
-        <f>E67+E68</f>
-        <v/>
-      </c>
-      <c r="F69" s="16">
-        <f>F67+F68</f>
-        <v/>
-      </c>
-      <c r="G69" s="16" t="n"/>
-      <c r="H69" s="16" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="14" t="inlineStr"/>
-      <c r="B71" s="14" t="inlineStr">
+      <c r="C71" s="16">
+        <f>C69+C70</f>
+        <v/>
+      </c>
+      <c r="D71" s="16" t="n"/>
+      <c r="E71" s="16">
+        <f>E69+E70</f>
+        <v/>
+      </c>
+      <c r="F71" s="16">
+        <f>F69+F70</f>
+        <v/>
+      </c>
+      <c r="G71" s="16" t="n"/>
+      <c r="H71" s="16" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="14" t="inlineStr"/>
+      <c r="B73" s="14" t="inlineStr">
         <is>
           <t>CONTINGENCY (30% of base, per DOE 413.3B / AACE Class 4)</t>
         </is>
       </c>
-      <c r="C71" s="14" t="n"/>
-      <c r="D71" s="14" t="n"/>
-      <c r="E71" s="14" t="n"/>
-      <c r="F71" s="14">
-        <f>F69*0.30</f>
-        <v/>
-      </c>
-      <c r="G71" s="14" t="n"/>
-      <c r="H71" s="14" t="inlineStr">
-        <is>
-          <t>AACE 18R-97 Class 4: typical accuracy range -15% to +30%. DOE Order 413.3B requires contingency at conceptual design. 30% applied to full project base.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="16" t="n"/>
-      <c r="B72" s="16" t="inlineStr">
+      <c r="C73" s="14" t="n"/>
+      <c r="D73" s="14" t="n"/>
+      <c r="E73" s="14" t="n"/>
+      <c r="F73" s="14">
+        <f>F71*0.30</f>
+        <v/>
+      </c>
+      <c r="G73" s="14" t="n"/>
+      <c r="H73" s="14" t="inlineStr">
+        <is>
+          <t>AACE 18R-97 Class 4: -15% to +30% accuracy. DOE 413.3B requires contingency at conceptual design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="16" t="n"/>
+      <c r="B74" s="16" t="inlineStr">
         <is>
           <t>TOTAL ESTIMATED COST (Base + Contingency)</t>
         </is>
       </c>
-      <c r="C72" s="16" t="n"/>
-      <c r="D72" s="16" t="n"/>
-      <c r="E72" s="16" t="n"/>
-      <c r="F72" s="16">
-        <f>F69+F71</f>
-        <v/>
-      </c>
-      <c r="G72" s="16" t="n"/>
-      <c r="H72" s="16" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="17" t="inlineStr">
-        <is>
-          <t>KEY ASSUMPTIONS &amp; RISKS</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Electrical based on Substation 507 option. Substation 502 option would add ~$7M to WBS 8.1.</t>
-        </is>
-      </c>
+      <c r="C74" s="16" t="n"/>
+      <c r="D74" s="16" t="n"/>
+      <c r="E74" s="16" t="n"/>
+      <c r="F74" s="16">
+        <f>F71+F73</f>
+        <v/>
+      </c>
+      <c r="G74" s="16" t="n"/>
+      <c r="H74" s="16" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>A2</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Circulator cost assumes new procurement. PEP-II 1.5 MW circulators may be reusable (saves ~$400k in WBS 2.3).</t>
+      <c r="A76" s="17" t="inlineStr">
+        <is>
+          <t>KEY ASSUMPTIONS</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SSA spares (WBS 1.2) assume 2 units. Could be reduced to 1 (saves $312k) or increased per ops requirements.</t>
+          <t>Electrical based on Substation 507 option. Substation 502 would add ~$7M to WBS 8.1.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Labor rate: $200/hr burdened (SLAC lab rate including overhead). 1 FTE = 1,740 hrs/yr.</t>
+          <t>Circulator cost assumes new procurement ($400k). PEP-II 1.5 MW circulators may be reusable (saves ~$400k).</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>RISK: Interface Chassis on critical path (design not started). PCB iteration may add 3-6 months and $10-20k.</t>
+          <t>2 SSA hot-swap spares included ($623k). Could reduce to 1 (saves $312k) or increase per ops.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>RISK: Tuner motor controller reliability unproven. May require redesign (adds $20-50k and 0.5 FTE).</t>
+          <t>Labor rate: $200/hr burdened (SLAC overhead-inclusive). 1 FTE = 1,740 hrs/yr.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>RISK: EPICS Coordinator software is largest untouched scope. Schedule risk if parallel development insufficient.</t>
+          <t>LLRF upgrade is prerequisite and funded separately. LLRF9 controllers, arc detection, waveform buffer, tuner controllers carry over.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>RISK: PPS regulatory approval timeline uncertain. Early engagement with AD Safety Division required.</t>
+          <t>NIP system required per SLAC ESH Chapter 50 (RF &amp; Microwave Safety) for new SSA building with &gt;1 kW RF sources.</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>RISK: DOE lab construction costs typically 50-100% higher than commercial. WBS 8.3 may be significantly understated.</t>
+      <c r="A83" s="17" t="inlineStr">
+        <is>
+          <t>KEY RISKS</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Interface Chassis on critical path (new SSA-specific design not started). PCB iteration may add 3-6 months.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>PPS redesign scope uncertain. 16-channel SSA safety chain more complex than single-klystron PPS. Safety review timeline unknown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>NIP system: first SSA installation at SPEAR. No prior RFSP template for this SSA configuration. Safety review may be lengthy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>EPICS Coordinator software largest untouched scope. Hot-swap logic and N-1 degradation are new SSA-specific requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>DOE lab construction costs typically 50-100% higher than commercial. WBS 8.3 may be significantly understated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
           <t>R6</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>RISK: Limited SPEAR testing windows. Integration testing constrained to summer shutdowns and brief maintenance periods.</t>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Limited SPEAR testing windows. Integration constrained to summer shutdowns and brief maintenance periods.</t>
         </is>
       </c>
     </row>
@@ -2377,7 +3086,1336 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>SPEAR3 SSA Upgrade - Reference Pricing &amp; Vendor Links</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>For procurement planning. Prices are indicative; formal quotes required before purchase.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>URL / Product Link</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Model / Part #</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Unit Price</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Date / Source</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>WBS 1.0 - SSA RF SOURCE</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="n"/>
+      <c r="C6" s="19" t="n"/>
+      <c r="D6" s="19" t="n"/>
+      <c r="E6" s="19" t="n"/>
+      <c r="F6" s="19" t="n"/>
+      <c r="G6" s="19" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>65 kW SSA Module (476.3 MHz CW)</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>R&amp;K Company (Japan)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>https://www.rk-microwave.com/</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Custom 65 kW SSA</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>$311,600</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>July 2025 quote</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>Includes internal 480V PS, LCW cooling, VSWR protection, Ethernet/serial control</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>SSA RF Dummy Load (50 kW CW)</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Bird Technologies / Mega Industries</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>https://www.birdrf.com/Products/RF-Loads.aspx</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Custom WR2100/coax load</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>$10-25k est.</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>For Bldg 122 test stand; water-cooled</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>WBS 2.0 - RF DISTRIBUTION &amp; COMBINING</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="n"/>
+      <c r="C10" s="19" t="n"/>
+      <c r="D10" s="19" t="n"/>
+      <c r="E10" s="19" t="n"/>
+      <c r="F10" s="19" t="n"/>
+      <c r="G10" s="19" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>WR2100 Waveguide (straight, bends, flex)</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Mega Industries</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>https://www.megaind.com/products/waveguide-sizes/wr2100-waveguide/</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>WR2100 (21x10.5 in)</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>$50-150/ft est.</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>Catalog</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>0.35-0.53 GHz, 205-290 MW peak rating, 0.188" wall. Also: Space Machine (space-machine.com)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>WR2100 Waveguide (catalog/3D models)</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Microwave Techniques (Mega subsidiary)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>https://catalog.microwavetechniques.com/viewitems/by-waveguide-component-size/wr2100</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Various</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>Catalog</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>Full 3D CAD catalog for WR2100 components: straights, bends, couplers, transitions, windows</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>WR2100 Directional Coupler</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Mega Industries</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>https://www.megaind.com/products/waveguide-sizes/wr2100-waveguide/</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>WR2100 coupler</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>$5-15k est.</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>Catalog</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>Various coupling ratios available. Also custom designs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>WR2100 Circulator (high power)</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Mega Industries / AFT Microwave</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>https://www.megaind.com/products/waveguide-sizes/wr2100-waveguide/</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>WR2100 circulator</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>$80-120k est.</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>Ferrite circulator for 250+ kW CW @ 476 MHz. AFT: aft-microwave.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>WR2100 High Power Load (water-cooled)</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Mega Industries</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>https://www.megaind.com/products/waveguide-sizes/wr2100-waveguide/</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>WR2100 load</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>$10-25k est.</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>Catalog</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>Water-cooled dummy load for circulator termination. 250+ kW CW rating.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>WR2100 Vacuum Window</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Mega Industries</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>https://www.megaind.com/products/waveguide-sizes/wr2100-waveguide/</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>WR2100 MegaSeal</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>Catalog</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>If needed at waveguide-to-cavity interface</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>6-1/8" Coaxial Combiner (4:1)</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>SPINNER Group / Custom</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>https://products.spinner-group.com/</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Custom 4-way combiner</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>$30-50k est.</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>6-1/8" EIA input, WR2100 output. SPINNER makes broadcast combiners; custom for accelerator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>WR2100-to-Coax Transition</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Mega Industries / Made-in-China</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>https://www.megaind.com/products/waveguide-sizes/wr2100-waveguide/</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>WR2100 transition</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>$500-5k</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>Catalog</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>WR2100 to 6-1/8" coax or N-type. Also: efinetech.en.made-in-china.com ($25-65 for adapter)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>Unistrut Channel &amp; Waveguide Hangers</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Unistrut / Atkore</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>https://www.unistrut.us/</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>P1000, P5500 series</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>$5-15/ft</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>Catalog</t>
+        </is>
+      </c>
+      <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>Standard Unistrut for waveguide support every 8 ft. WR2100 ~10 lb/ft.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>WBS 3.0 - CONTROL ELECTRONICS &amp; PROTECTION</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="n"/>
+      <c r="C21" s="19" t="n"/>
+      <c r="D21" s="19" t="n"/>
+      <c r="E21" s="19" t="n"/>
+      <c r="F21" s="19" t="n"/>
+      <c r="G21" s="19" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>Dimtel LLRF9/500 Controller</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>Dimtel, Inc.</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>https://www.dimtel.com/products/llrf9</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>LLRF9/500</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>$117,000 list</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>Vendor quote</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>9-ch LLRF controller. 15% vol discount = $99,450. SSA project: reconfiguration only (hardware from LLRF upgrade)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>Dimtel LLRF9/500 Specifications</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>Dimtel, Inc.</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>https://www.dimtel.com/products/specs/llrf9_500</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>LLRF9/500</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>See above</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>Spec sheet</t>
+        </is>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>500 MHz center, 6 MHz BW, 9 RF inputs, FPGA interlocks, EPICS IOC built-in</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>AB CompactLogix Controller</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>Rockwell Automation</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>https://www.rockwellautomation.com/</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>5069-L320ER</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>$3,692</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>TaskListRev3</t>
+        </is>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>2MB Ethernet controller. See IQElectro, IndustrialAutomationCo for distributor pricing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>AB Output Module (8-pt analog)</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>Rockwell Automation</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>https://www.rockwellautomation.com/</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>5069-OF8</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>$1,536</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>TaskListRev3</t>
+        </is>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>Analog output. Qty 3 per MPS set = $4,607</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>AB Isolated Relay Output</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>Rockwell Automation</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>https://www.rockwellautomation.com/</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>5069-OX41</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>$452</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>TaskListRev3</t>
+        </is>
+      </c>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>Qty 10 per MPS set = $4,516</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>AB Universal Analog Input</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>Rockwell Automation</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>https://www.rockwellautomation.com/</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>5069-IY4</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>$521</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>TaskListRev3</t>
+        </is>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>Qty 2 per set = $1,043</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>AB Analog Input (8-ch)</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>Rockwell Automation</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>https://www.rockwellautomation.com/</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>5069-IF8</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>$876</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>TaskListRev3</t>
+        </is>
+      </c>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
+          <t>Qty 2 per set = $1,752</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>AB DC Input (16-pt)</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>Rockwell Automation</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>https://www.rockwellautomation.com/</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>5069-IB16</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>$266</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>TaskListRev3</t>
+        </is>
+      </c>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>Qty 4 per set = $1,063</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>AB Spring RTB (18-pt)</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>Rockwell Automation</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>https://www.rockwellautomation.com/</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>5069-RTB18-SPRING</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>$62</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>TaskListRev3</t>
+        </is>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>Removable terminal blocks. Qty 25 = $1,561</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>Complete ControlLogix PLC Set</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>Rockwell Automation</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr"/>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>See above BOM</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>$21,994/set</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>TaskListRev3</t>
+        </is>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
+        <is>
+          <t>Detailed BOM from LLRFUpgradeTaskListRev3.docx. SSA needs expanded I/O.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>Galil 4-Axis Motion Controller</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>Galil Motion Control</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>https://www.galil.com/node/1486</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>DMC-4143</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>$1,675</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>Galil website</t>
+        </is>
+      </c>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
+          <t>4-axis Ethernet/USB. 100-qty price: $1,115. For cavity tuner control.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>Microstep-MIS Arc Sensor</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>MicroStep-MIS</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>https://microstep-mis.com/web/products?category=radiation+&amp;product=waveguide_arc_detector</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>Optical sensor</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>470 EUR ea</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>Nov 2024 quote</t>
+        </is>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>10 sensors needed. Quote from Erik Bystricky.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>Microstep-MIS Arc Receiver</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>MicroStep-MIS</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>https://microstep-mis.com/web/products?category=radiation+&amp;product=waveguide_arc_detector</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>Process unit</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>635 EUR ea</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>Nov 2024 quote</t>
+        </is>
+      </c>
+      <c r="G34" s="11" t="inlineStr">
+        <is>
+          <t>6 receivers (5 active + 1 spare). Handles 2 sensors each.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>Microstep-MIS Interconnect Cable (2m)</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>MicroStep-MIS</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>https://microstep-mis.com/</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>Fiber cable</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>186 EUR ea</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>Nov 2024 quote</t>
+        </is>
+      </c>
+      <c r="G35" s="11" t="inlineStr">
+        <is>
+          <t>5 cables needed. Sensor-to-receiver connection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>MCL RF Power Detector</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>Mini-Circuits</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="inlineStr">
+        <is>
+          <t>https://www.minicircuits.com/</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>ZX47-40LN-S+</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>$105 ea</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="inlineStr">
+        <is>
+          <t>TaskListRev3</t>
+        </is>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>Log detector for waveform buffer. 10 qty = $1,050. SMA connectors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>MCL SMA Adapter</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>Mini-Circuits</t>
+        </is>
+      </c>
+      <c r="C37" s="20" t="inlineStr">
+        <is>
+          <t>https://www.minicircuits.com/</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>SF-SF50+ / NFFL-SF50+</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>$6-30 ea</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr">
+        <is>
+          <t>TaskListRev3</t>
+        </is>
+      </c>
+      <c r="G37" s="11" t="inlineStr">
+        <is>
+          <t>SMA bulkhead adapters, N-to-SMA adapters</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>WBS 3.8-3.9 - SAFETY SYSTEMS (PPS, NIP)</t>
+        </is>
+      </c>
+      <c r="B39" s="19" t="n"/>
+      <c r="C39" s="19" t="n"/>
+      <c r="D39" s="19" t="n"/>
+      <c r="E39" s="19" t="n"/>
+      <c r="F39" s="19" t="n"/>
+      <c r="G39" s="19" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>RF Field Monitor / Sensor</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>Narda Safety Test Solutions</t>
+        </is>
+      </c>
+      <c r="C40" s="20" t="inlineStr">
+        <is>
+          <t>https://www.narda-sts.com/</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>RadMan 2 / Area Monitor</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>$3-8k ea</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t>Personal/area RF exposure monitors. For NIP system per SLAC ESH Ch.50.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>RF Safety Interlock Controller</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>Various / Custom</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr"/>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>PLC-based or dedicated</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>$10-15k</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="G41" s="11" t="inlineStr">
+        <is>
+          <t>Door interlocks, emergency stops, RF enable/disable logic. May use AB CompactLogix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>RF Warning Beacons &amp; Signage</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>Federal Signal / OSHA-compliant</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr"/>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>Warning lights + signs</t>
+        </is>
+      </c>
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>$2-5k</t>
+        </is>
+      </c>
+      <c r="F42" s="11" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="G42" s="11" t="inlineStr">
+        <is>
+          <t>SLAC ESH Ch.50 requires visible/audible warnings when RF active in accessible areas</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>SLAC ESH Chapter 50 (RF Safety)</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>SLAC ES&amp;H Division</t>
+        </is>
+      </c>
+      <c r="C43" s="20" t="inlineStr">
+        <is>
+          <t>https://esh.slac.stanford.edu/hazardous_activities/rf</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr">
+        <is>
+          <t>May 2024</t>
+        </is>
+      </c>
+      <c r="G43" s="11" t="inlineStr">
+        <is>
+          <t>Program manager: Mike McDaniel. Governs all RF sources &gt;1W at SLAC. IEEE C95.1 based.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>OSHA 1910.97 (Nonionizing Radiation)</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>OSHA</t>
+        </is>
+      </c>
+      <c r="C44" s="20" t="inlineStr">
+        <is>
+          <t>https://www.osha.gov/laws-regs/regulations/standardnumber/1910/1910.97</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="inlineStr">
+        <is>
+          <t>Federal reg</t>
+        </is>
+      </c>
+      <c r="G44" s="11" t="inlineStr">
+        <is>
+          <t>Federal standard for electromagnetic radiation exposure limits</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId29"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2936,7 +4974,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/SSA_upgrade/SSA Upgrade Project Cost V1.xlsx
+++ b/SSA_upgrade/SSA Upgrade Project Cost V1.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -89,6 +89,9 @@
     <font>
       <i val="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
     </font>
   </fonts>
   <fills count="7">
@@ -162,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="2"/>
@@ -195,6 +198,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -551,6 +555,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="17" t="inlineStr">
         <is>
@@ -579,6 +584,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="21" t="inlineStr">
         <is>
@@ -593,6 +599,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
         <is>
@@ -649,6 +656,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="17" t="inlineStr">
         <is>
@@ -656,6 +664,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="22" t="inlineStr">
         <is>
@@ -684,6 +693,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="22" t="inlineStr">
         <is>
@@ -719,6 +729,7 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="22" t="inlineStr">
         <is>
@@ -789,6 +800,7 @@
         </is>
       </c>
     </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" s="22" t="inlineStr">
         <is>
@@ -831,6 +843,7 @@
         </is>
       </c>
     </row>
+    <row r="50"/>
     <row r="51">
       <c r="A51" s="22" t="inlineStr">
         <is>
@@ -873,6 +886,7 @@
         </is>
       </c>
     </row>
+    <row r="57"/>
     <row r="58">
       <c r="A58" s="22" t="inlineStr">
         <is>
@@ -901,6 +915,7 @@
         </is>
       </c>
     </row>
+    <row r="62"/>
     <row r="63">
       <c r="A63" s="22" t="inlineStr">
         <is>
@@ -922,17 +937,19 @@
         </is>
       </c>
     </row>
+    <row r="66"/>
     <row r="67">
       <c r="A67" s="17" t="inlineStr">
         <is>
-          <t>4. NOT INCLUDED IN SSA PROJECT SCOPE (reference items or other groups)</t>
-        </is>
-      </c>
-    </row>
+          <t>4. SUPPORTING SCOPE ITEMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="68"/>
     <row r="69">
       <c r="A69" s="22" t="inlineStr">
         <is>
-          <t>4a. Infrastructure (WBS 8.0 - F&amp;O / Facilities scope)</t>
+          <t>4a. Infrastructure (WBS 8.0 - Included in SSA Project)</t>
         </is>
       </c>
     </row>
@@ -960,10 +977,11 @@
     <row r="73">
       <c r="A73" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  These are carried as REFERENCE items for total project budgeting.</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">  These are INCLUDED in the SSA project scope and cost estimate (WBS 8.0).</t>
+        </is>
+      </c>
+    </row>
+    <row r="74"/>
     <row r="75">
       <c r="A75" s="22" t="inlineStr">
         <is>
@@ -1006,6 +1024,7 @@
         </is>
       </c>
     </row>
+    <row r="81"/>
     <row r="82">
       <c r="A82" s="22" t="inlineStr">
         <is>
@@ -1041,6 +1060,7 @@
         </is>
       </c>
     </row>
+    <row r="87"/>
     <row r="88">
       <c r="A88" s="17" t="inlineStr">
         <is>
@@ -1097,6 +1117,7 @@
         </is>
       </c>
     </row>
+    <row r="96"/>
     <row r="97">
       <c r="A97" s="17" t="inlineStr">
         <is>
@@ -1180,7 +1201,7 @@
     <row r="3">
       <c r="A3" s="18" t="inlineStr">
         <is>
-          <t>NOTE: This estimate covers SSA upgrade scope ONLY. LLRF upgrade (klystron/HVPS controls modernization) is a prerequisite project funded separately.</t>
+          <t>NOTE: This estimate covers SSA upgrade scope including infrastructure (WBS 1-8). LLRF upgrade (klystron/HVPS controls modernization) is a prerequisite project funded separately.</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2702,7 @@
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>INFRASTRUCTURE (Reference - F&amp;O / other groups' scope)</t>
+          <t>INFRASTRUCTURE (Included in SSA Project Scope)</t>
         </is>
       </c>
       <c r="C63" s="10" t="n"/>
@@ -2721,7 +2742,7 @@
       </c>
       <c r="H64" s="13" t="inlineStr">
         <is>
-          <t>REF: Sub 507 option ($1-2M per 1/27 mtg). 2.5-3 MVA transformer, 12kV feed, 480V panels for 16 SSAs. Alt: Sub 502 = $8-9M.</t>
+          <t>Sub 507 option ($1-2M per 1/27 mtg). 2.5-3 MVA transformer, 12kV feed, 480V panels for 16 SSAs. Alt: Sub 502 = $8-9M.</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2776,7 @@
       </c>
       <c r="H65" s="13" t="inlineStr">
         <is>
-          <t>REF: 400 GPM LCW for 4 SSA stations. Option B: new 6"+ connection (per 3/10 mtg). Summer shutdown required.</t>
+          <t>400 GPM LCW for 4 SSA stations. Option B: new 6"+ connection (per 3/10 mtg). Summer shutdown required.</t>
         </is>
       </c>
     </row>
@@ -2789,7 +2810,7 @@
       </c>
       <c r="H66" s="13" t="inlineStr">
         <is>
-          <t>REF: ~636 sqft + ~300 sqft mezzanine @ 27 ft. Two-story layout (per 2/24 mtg). OSHA stairway. Roll-up doors. Seismic. F&amp;O prior estimate $1.3M.</t>
+          <t>~636 sqft + ~300 sqft mezzanine @ 27 ft. Two-story layout (per 2/24 mtg). OSHA stairway. Roll-up doors. Seismic. F&amp;O prior estimate $1.3M.</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2818,7 @@
       <c r="A67" s="12" t="inlineStr"/>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>Subtotal WBS 8.0 (Reference)</t>
+          <t>Subtotal WBS 8.0 (Infrastructure)</t>
         </is>
       </c>
       <c r="C67" s="12">
@@ -2843,7 +2864,7 @@
       <c r="A70" s="14" t="n"/>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>INFRASTRUCTURE REFERENCE (WBS 8)</t>
+          <t>INFRASTRUCTURE SCOPE (WBS 8)</t>
         </is>
       </c>
       <c r="C70" s="14">
@@ -3065,7 +3086,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>DOE lab construction costs typically 50-100% higher than commercial. WBS 8.3 may be significantly understated.</t>
+          <t>DOE lab construction costs typically 50-100% higher than commercial. WBS 8.3 building estimate based on F&amp;O prior study ($1.3M); actual cost TBD per CD-1 design.</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3208,22 +3229,22 @@
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>SSA RF Dummy Load (50 kW CW)</t>
+          <t>SSA RF Dummy Load (250 kW CW, water-cooled)</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Bird Technologies / Mega Industries</t>
+          <t>Ferrite Microwave Technologies (FMT)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>https://www.birdrf.com/Products/RF-Loads.aspx</t>
+          <t>https://ferriteinc.com/high-power-waveguide-terminations/water-cooled-loads/</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Custom WR2100/coax load</t>
+          <t>Custom WR2100 water-cooled load</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -3233,12 +3254,12 @@
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>Estimate</t>
+          <t>Vendor catalog (verified)</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
-          <t>For Bldg 122 test stand; water-cooled</t>
+          <t>FMT: WR28-WR2300 waveguide loads, 50 MHz-50 GHz. MIL-D-3954 compliant. Ultra-high temp refractory ceramic absorber. REPLACES Bird Technologies (max 20 kW, unsuitable).</t>
         </is>
       </c>
     </row>
@@ -3369,22 +3390,22 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>WR2100 Circulator (high power)</t>
+          <t>WR2100 Circulator (250+ kW CW @ 476 MHz)</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Mega Industries / AFT Microwave</t>
+          <t>Ferrite Microwave Technologies (FMT)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>https://www.megaind.com/products/waveguide-sizes/wr2100-waveguide/</t>
+          <t>https://ferriteinc.com/high-power-microwave-circulators-isolators/waveguide-circulators/</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>WR2100 circulator</t>
+          <t>Custom WR2100 3-port circulator</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -3394,34 +3415,34 @@
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>Estimate</t>
+          <t>Vendor inquiry (verified)</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
-          <t>Ferrite circulator for 250+ kW CW @ 476 MHz. AFT: aft-microwave.com</t>
+          <t>FMT: 1400+ circulator designs, WR28-WR2300, 50 MHz-50 GHz, 5W to 50+ MW. Scientific/accelerator specialist. AFT Microwave (aft-microwave.com) as alternate (L/S/C/X bands; confirm 476 MHz coverage before ordering).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>WR2100 High Power Load (water-cooled)</t>
+          <t>WR2100 High-Power Water-Cooled Load (circulator termination)</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Mega Industries</t>
+          <t>Ferrite Microwave Technologies (FMT) / MCI Broadcast</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>https://www.megaind.com/products/waveguide-sizes/wr2100-waveguide/</t>
+          <t>https://ferriteinc.com/high-power-waveguide-terminations/water-cooled-loads/</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>WR2100 load</t>
+          <t>WR2100 water load, 250+ kW CW</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
@@ -3431,12 +3452,12 @@
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>Catalog</t>
+          <t>Vendor catalog (verified)</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>Water-cooled dummy load for circulator termination. 250+ kW CW rating.</t>
+          <t>For circulator port 3 termination. FMT water-cooled loads: refractory ceramic absorber, welded aluminum housing. MCI Broadcast (mcibroadcast.com) also makes accelerator-specific waveguide loads 0.32-10 GHz.</t>
         </is>
       </c>
     </row>
@@ -3480,22 +3501,22 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>6-1/8" Coaxial Combiner (4:1)</t>
+          <t>4:1 High-Power Waveguide Combiner (320 kW @ 476 MHz)</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>SPINNER Group / Custom</t>
+          <t>Mega Industries</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>https://products.spinner-group.com/</t>
+          <t>https://www.megaind.com/high-power-waveguide-combiners-for-sspa/</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Custom 4-way combiner</t>
+          <t>Custom WR2100 4:1 combiner (ref: WR1800 NSLS-II design)</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
@@ -3505,12 +3526,12 @@
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>Estimate</t>
+          <t>Vendor reference (verified)</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
-          <t>6-1/8" EIA input, WR2100 output. SPINNER makes broadcast combiners; custom for accelerator.</t>
+          <t>PRECEDENT: Mega built WR1800 4:1 combiner for NSLS-II at Brookhaven (500 MHz, 4×80kW=320kW, &lt;0.12 dB loss, &lt;1.18:1 VSWR). Nearly identical to SPEAR3 application (476 MHz, 4×65kW=260kW). REPLACES SPINNER Group (max 8.8 kW broadcast-grade, unsuitable).</t>
         </is>
       </c>
     </row>
@@ -4376,6 +4397,97 @@
       <c r="G44" s="11" t="inlineStr">
         <is>
           <t>Federal standard for electromagnetic radiation exposure limits</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="22" t="inlineStr">
+        <is>
+          <t>VENDOR VERIFICATION NOTES (March 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="24" t="inlineStr">
+        <is>
+          <t>Bird Technologies</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>REMOVED — Max power 20 kW (8740 Series). Unsuitable for 250+ kW circulator loads. Replaced by FMT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="24" t="inlineStr">
+        <is>
+          <t>SPINNER Group</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>REMOVED — Broadcast-grade combiners (8.8 kW max @ 80.5 MHz). Unsuitable for 260 kW @ 476 MHz. Replaced by Mega Industries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="24" t="inlineStr">
+        <is>
+          <t>AFT Microwave</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CAUTION — Products focus L/S/C/X bands (GHz range). Confirm 476 MHz coverage before ordering. FMT is preferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="24" t="inlineStr">
+        <is>
+          <t>Ferrite Microwave Technologies (FMT)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ADDED — WR28-WR2300, 50 MHz-50 GHz, 1400+ designs. Accelerator specialist. Loads + circulators.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="24" t="inlineStr">
+        <is>
+          <t>Mega Industries SSPA Combiner</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ADDED — NSLS-II precedent: 4×80kW=320kW @ 500 MHz (Brookhaven). Nearly identical to SPEAR3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="24" t="inlineStr">
+        <is>
+          <t>MCI Broadcast</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ADDED — Micro Communications waveguide loads for particle accelerators, 0.32-10 GHz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="24" t="inlineStr">
+        <is>
+          <t>All other vendors</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>VERIFIED — Links confirmed active, components confirmed suitable for 476.3 MHz / WR2100 / high-power CW.</t>
         </is>
       </c>
     </row>

--- a/SSA_upgrade/SSA Upgrade Project Cost V1.xlsx
+++ b/SSA_upgrade/SSA Upgrade Project Cost V1.xlsx
@@ -165,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="2"/>
@@ -199,6 +199,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -542,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A102"/>
+  <dimension ref="A1:A110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -555,7 +557,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="17" t="inlineStr">
         <is>
@@ -584,7 +585,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="21" t="inlineStr">
         <is>
@@ -599,18 +599,17 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
         <is>
-          <t>2. PREREQUISITE</t>
+          <t>2. RELATED PROJECT (LLRF Upgrade — Independent, Separate Scope)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="22" t="inlineStr">
         <is>
-          <t>The LLRF upgrade project (separate scope, separately funded) must be completed first.</t>
+          <t>The LLRF upgrade project (separate scope, separately funded) is underway independently.</t>
         </is>
       </c>
     </row>
@@ -652,11 +651,10 @@
     <row r="18">
       <c r="A18" s="21" t="inlineStr">
         <is>
-          <t>The SSA upgrade builds upon this modernized controls platform.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
+          <t>The SSA upgrade leverages shared hardware where practical but is not dependent on LLRF completion.</t>
+        </is>
+      </c>
+    </row>
     <row r="20">
       <c r="A20" s="17" t="inlineStr">
         <is>
@@ -664,7 +662,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="22" t="inlineStr">
         <is>
@@ -693,7 +690,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="22" t="inlineStr">
         <is>
@@ -729,7 +725,6 @@
         </is>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" s="22" t="inlineStr">
         <is>
@@ -800,7 +795,6 @@
         </is>
       </c>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="A44" s="22" t="inlineStr">
         <is>
@@ -843,7 +837,6 @@
         </is>
       </c>
     </row>
-    <row r="50"/>
     <row r="51">
       <c r="A51" s="22" t="inlineStr">
         <is>
@@ -886,7 +879,6 @@
         </is>
       </c>
     </row>
-    <row r="57"/>
     <row r="58">
       <c r="A58" s="22" t="inlineStr">
         <is>
@@ -915,7 +907,6 @@
         </is>
       </c>
     </row>
-    <row r="62"/>
     <row r="63">
       <c r="A63" s="22" t="inlineStr">
         <is>
@@ -937,224 +928,274 @@
         </is>
       </c>
     </row>
-    <row r="66"/>
     <row r="67">
-      <c r="A67" s="17" t="inlineStr">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>3h. Decommissioning — Existing RF Station (WBS 9.0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Klystron removal (Marconi K3512S, 1.2 MW CW, ~8-10 tons with solenoid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - HVPS removal (2.5 MVA: SCR rectifier, oil-insulated 12.47 kV transformer, crowbar circuit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Waveguide network removal (WR2100 from klystron to tunnel, magic tee 4-way splitter on roof)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Circulator and RF loads removal, HCW cooling system drain/flush</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Lead shielding removal and hazardous waste abatement (EPA/RCRA classified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Crane/rigging services, environmental compliance, radiological clearance survey</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="17" t="inlineStr">
         <is>
           <t>4. SUPPORTING SCOPE ITEMS</t>
         </is>
       </c>
     </row>
-    <row r="68"/>
-    <row r="69">
-      <c r="A69" s="22" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="22" t="inlineStr">
         <is>
           <t>4a. Infrastructure (WBS 8.0 - Included in SSA Project)</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 480 VAC distribution system (Substation 507 upgrade, 2.5-3 MVA transformer)</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - Cooling water upgrade (400 GPM LCW for SSA stations)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - Building extension and mezzanine (~636 + 300 sqft, two-story)</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  These are INCLUDED in the SSA project scope and cost estimate (WBS 8.0).</t>
-        </is>
-      </c>
-    </row>
-    <row r="74"/>
-    <row r="75">
-      <c r="A75" s="22" t="inlineStr">
-        <is>
-          <t>4b. LLRF Upgrade (separate project, prerequisite)</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - LLRF9 controller procurement and installation</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - HVPS controller modernization (CompactLogix)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Original Interface Chassis design for klystron topology</t>
+          <t xml:space="preserve">  - 480 VAC distribution system (Substation 507 upgrade, 2.5-3 MVA transformer)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Legacy software migration (SNL -&gt; Python/EPICS)</t>
+          <t xml:space="preserve">  - Cooling water upgrade (400 GPM LCW for SSA stations)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Klystron heater controller upgrade</t>
-        </is>
-      </c>
-    </row>
-    <row r="81"/>
-    <row r="82">
-      <c r="A82" s="22" t="inlineStr">
-        <is>
-          <t>4c. Items eliminated by SSA upgrade</t>
+          <t xml:space="preserve">  - Building extension and mezzanine (~636 + 300 sqft, two-story)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  These are INCLUDED in the SSA project scope and cost estimate (WBS 8.0).</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - HVPS (High Voltage Power Supply) - SSAs use internal 480V supplies</t>
+      <c r="A83" s="22" t="inlineStr">
+        <is>
+          <t>4b. LLRF Upgrade (separate, independent project)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Klystron - replaced by SSA modules</t>
+          <t xml:space="preserve">  - LLRF9 controller procurement and installation</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Klystron cathode heater - not applicable to SSAs</t>
+          <t xml:space="preserve">  - HVPS controller modernization (CompactLogix)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Drive amplifier - SSAs are self-contained</t>
-        </is>
-      </c>
-    </row>
-    <row r="87"/>
+          <t xml:space="preserve">  - Original Interface Chassis design for klystron topology</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Legacy software migration (SNL -&gt; Python/EPICS)</t>
+        </is>
+      </c>
+    </row>
     <row r="88">
-      <c r="A88" s="17" t="inlineStr">
-        <is>
-          <t>5. KEY TECHNICAL PARAMETERS</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - Operating frequency: 476.3 MHz</t>
+      <c r="A88" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Klystron heater controller upgrade</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - Total RF power: 16 x 65 kW = 1,040 kW</t>
+      <c r="A90" s="22" t="inlineStr">
+        <is>
+          <t>4c. Items eliminated and decommissioned by SSA upgrade</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - RF cavities: 4 (SPEAR3 storage ring)</t>
+          <t xml:space="preserve">  - HVPS (2.5 MVA, oil-insulated) — SSAs use internal 480V supplies; HVPS decommissioned in WBS 9.0</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - SSA per cavity: 4 modules combined via 4:1 coaxial combiner</t>
+          <t xml:space="preserve">  - Klystron (Marconi K3512S, 1.2 MW CW) — replaced by 16 SSA modules; decommissioned in WBS 9.0</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Waveguide: WR2100 (lambda_g = 80.4 cm at 476.3 MHz)</t>
+          <t xml:space="preserve">  - Klystron cathode heater — not applicable to SSAs</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Cooling: LCW, 400 GPM total (~100 GPM/station, deltaT ~10K)</t>
+          <t xml:space="preserve">  - Drive amplifier — SSAs are self-contained</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - SSA building: two-story, ~936 sqft total, 27 ft height, 9 ft clear under platform</t>
-        </is>
-      </c>
-    </row>
-    <row r="96"/>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Magic tee 4-way splitter — replaced by 4 independent SSA-to-cavity waveguide runs</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="17" t="inlineStr">
+        <is>
+          <t>5. KEY TECHNICAL PARAMETERS</t>
+        </is>
+      </c>
+    </row>
     <row r="97">
-      <c r="A97" s="17" t="inlineStr">
-        <is>
-          <t>6. PROJECT TIMELINE (ESTIMATED)</t>
+      <c r="A97" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Operating frequency: 476.3 MHz</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Overall: ~6-7 years, completion ~2032-2033</t>
+          <t xml:space="preserve">  - Total RF power: 16 x 65 kW = 1,040 kW</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Strongly dependent on Substation 507 upgrade schedule</t>
+          <t xml:space="preserve">  - RF cavities: 4 (SPEAR3 storage ring)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Test stand procurement can begin near-term</t>
+          <t xml:space="preserve">  - SSA per cavity: 4 modules combined via 4:1 coaxial combiner</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Facility design/construction constrained by engineering resources</t>
+          <t xml:space="preserve">  - Waveguide: WR2100 (lambda_g = 80.4 cm at 476.3 MHz)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Cooling: LCW, 400 GPM total (~100 GPM/station, deltaT ~10K)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - SSA building: two-story, ~936 sqft total, 27 ft height, 9 ft clear under platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="17" t="inlineStr">
+        <is>
+          <t>6. PROJECT TIMELINE (ESTIMATED)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Overall: ~6-7 years, completion ~2032-2033</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Strongly dependent on Substation 507 upgrade schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Test stand procurement can begin near-term</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Facility design/construction constrained by engineering resources</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  - Integration testing limited to SPEAR summer shutdown windows (6-8 weeks)</t>
         </is>
@@ -1171,7 +1212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H89"/>
+  <dimension ref="A1:H117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1201,7 +1242,7 @@
     <row r="3">
       <c r="A3" s="18" t="inlineStr">
         <is>
-          <t>NOTE: This estimate covers SSA upgrade scope including infrastructure (WBS 1-8). LLRF upgrade (klystron/HVPS controls modernization) is a prerequisite project funded separately.</t>
+          <t>NOTE: This estimate covers SSA upgrade scope including infrastructure and decommissioning (WBS 1-9). The LLRF upgrade is a separate, independent project with no dependency relationship.</t>
         </is>
       </c>
     </row>
@@ -2838,270 +2879,595 @@
       <c r="H67" s="12" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="14" t="n"/>
-      <c r="B69" s="14" t="inlineStr">
-        <is>
-          <t>RF/CONTROLS SCOPE SUBTOTAL (WBS 1-7)</t>
-        </is>
-      </c>
-      <c r="C69" s="14">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>DECOMMISSIONING — EXISTING RF STATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Klystron Removal &amp; Disposal</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>15</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E70" t="n">
+        <v>87</v>
+      </c>
+      <c r="F70" t="n">
+        <v>102</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Remove Marconi K3512S 1.2 MW klystron (~8-10 tons with solenoid). LOTO, de-energize RF, disconnect WR2100 waveguide, LCW cooling, HV connections. Crane lift from klystron room. Disposal per SLAC waste procedures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>9.2</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>HVPS/Modulator Removal &amp; Oil Disposal</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>20</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E71" t="n">
+        <v>87</v>
+      </c>
+      <c r="F71" t="n">
+        <v>107</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Remove 2.5 MVA HVPS: SCR-controlled rectifier, 12.47 kV transformer (oil-insulated), crowbar circuit, HV bus. Drain/dispose transformer oil (~300-500 gal, test for PCBs). Disconnect 12.47 kV primary feed. Crane required for transformer (~5-10 tons).</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Waveguide Network &amp; Magic Tee Removal</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>10</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E72" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="F72" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Remove existing WR2100 waveguide from klystron to tunnel roof. Depressurize dry-air system. Remove magic tee 4-way splitter on roof (per 2/24 mtg: roof splitters removed). Disassemble flanged connections, lower sections. ~10 lb/ft waveguide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Circulator, RF Loads &amp; Ancillary Components</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>5</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E73" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="F73" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Remove existing AFT circulator (high-power ferrite, ~1-2 tons), HCW-cooled magic loads, circulator loads. Disconnect HCW cooling lines, drain/flush. Existing PEP-II circulators may be retained if usable for SSA (per 2/24 mtg).</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Lead Shielding Removal &amp; Hazmat Abatement</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>25</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E74" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="F74" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Remove lead shielding around klystron/HVPS area. Lead is classified hazardous waste (EPA/RCRA). Requires certified hazmat crew. Radiological survey of klystron area for activation products (per SLAC RP procedures). M&amp;S for disposal containers, transport.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Crane/Rigging Services &amp; Environmental Compliance</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>50</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E75" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="F75" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Crane rental (100-ton, ~$5-15k/day for 3-5 days) for klystron, HVPS transformer, heavy waveguide. Rigging contractor. PCB testing of transformer oil. Radiological clearance survey. Environmental compliance documentation per SLAC ES&amp;H. Waste manifests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>Subtotal WBS 9.0 (Decommissioning)</t>
+        </is>
+      </c>
+      <c r="C77">
+        <f>SUM(C70:C75)</f>
+        <v/>
+      </c>
+      <c r="E77">
+        <f>SUM(E70:E75)</f>
+        <v/>
+      </c>
+      <c r="F77">
+        <f>SUM(F70:F75)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="14" t="n"/>
+      <c r="B83" s="14" t="inlineStr">
+        <is>
+          <t>RF/CONTROLS SCOPE (WBS 1-7)</t>
+        </is>
+      </c>
+      <c r="C83" s="14">
         <f>C12+C21+C34+C42+C50+C56+C61</f>
         <v/>
       </c>
-      <c r="D69" s="14" t="n"/>
-      <c r="E69" s="14">
+      <c r="D83" s="14" t="n"/>
+      <c r="E83" s="14">
         <f>E12+E21+E34+E42+E50+E56+E61</f>
         <v/>
       </c>
-      <c r="F69" s="14">
+      <c r="F83" s="14">
         <f>F12+F21+F34+F42+F50+F56+F61</f>
         <v/>
       </c>
-      <c r="G69" s="14" t="n"/>
-      <c r="H69" s="14" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="14" t="n"/>
-      <c r="B70" s="14" t="inlineStr">
+      <c r="G83" s="14" t="n"/>
+      <c r="H83" s="14" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="14" t="n"/>
+      <c r="B84" s="14" t="inlineStr">
         <is>
           <t>INFRASTRUCTURE SCOPE (WBS 8)</t>
         </is>
       </c>
-      <c r="C70" s="14">
+      <c r="C84" s="14">
         <f>C67</f>
         <v/>
       </c>
-      <c r="D70" s="14" t="n"/>
-      <c r="E70" s="14">
+      <c r="D84" s="14" t="n"/>
+      <c r="E84" s="14">
         <f>E67</f>
         <v/>
       </c>
-      <c r="F70" s="14">
+      <c r="F84" s="14">
         <f>F67</f>
         <v/>
       </c>
-      <c r="G70" s="14" t="n"/>
-      <c r="H70" s="14" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="16" t="n"/>
-      <c r="B71" s="16" t="inlineStr">
-        <is>
-          <t>PROJECT BASE ESTIMATE (WBS 1-8)</t>
-        </is>
-      </c>
-      <c r="C71" s="16">
-        <f>C69+C70</f>
-        <v/>
-      </c>
-      <c r="D71" s="16" t="n"/>
-      <c r="E71" s="16">
-        <f>E69+E70</f>
-        <v/>
-      </c>
-      <c r="F71" s="16">
-        <f>F69+F70</f>
-        <v/>
-      </c>
-      <c r="G71" s="16" t="n"/>
-      <c r="H71" s="16" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="14" t="inlineStr"/>
-      <c r="B73" s="14" t="inlineStr">
+      <c r="G84" s="14" t="n"/>
+      <c r="H84" s="14" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="16" t="n"/>
+      <c r="B85" s="25" t="inlineStr">
+        <is>
+          <t>DECOMMISSIONING SCOPE (WBS 9)</t>
+        </is>
+      </c>
+      <c r="C85" s="16">
+        <f>C77</f>
+        <v/>
+      </c>
+      <c r="D85" s="16" t="n"/>
+      <c r="E85" s="16">
+        <f>E77</f>
+        <v/>
+      </c>
+      <c r="F85" s="16">
+        <f>F77</f>
+        <v/>
+      </c>
+      <c r="G85" s="16" t="n"/>
+      <c r="H85" s="16" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="14" t="inlineStr"/>
+      <c r="B87" s="26" t="inlineStr">
+        <is>
+          <t>PROJECT BASE ESTIMATE (WBS 1-9)</t>
+        </is>
+      </c>
+      <c r="C87" s="14">
+        <f>C83+C84+C85</f>
+        <v/>
+      </c>
+      <c r="D87" s="14" t="n"/>
+      <c r="E87" s="14">
+        <f>E83+E84+E85</f>
+        <v/>
+      </c>
+      <c r="F87" s="14">
+        <f>F83+F84+F85</f>
+        <v/>
+      </c>
+      <c r="G87" s="14" t="n"/>
+      <c r="H87" s="14" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="16" t="n"/>
+      <c r="B88" s="16" t="n"/>
+      <c r="C88" s="16" t="n"/>
+      <c r="D88" s="16" t="n"/>
+      <c r="E88" s="16" t="n"/>
+      <c r="F88" s="16" t="n"/>
+      <c r="G88" s="16" t="n"/>
+      <c r="H88" s="16" t="n"/>
+    </row>
+    <row r="89">
+      <c r="B89" t="inlineStr">
         <is>
           <t>CONTINGENCY (30% of base, per DOE 413.3B / AACE Class 4)</t>
         </is>
       </c>
-      <c r="C73" s="14" t="n"/>
-      <c r="D73" s="14" t="n"/>
-      <c r="E73" s="14" t="n"/>
-      <c r="F73" s="14">
-        <f>F71*0.30</f>
-        <v/>
-      </c>
-      <c r="G73" s="14" t="n"/>
-      <c r="H73" s="14" t="inlineStr">
+      <c r="F89">
+        <f>F87*0.30</f>
+        <v/>
+      </c>
+      <c r="H89" t="inlineStr">
         <is>
           <t>AACE 18R-97 Class 4: -15% to +30% accuracy. DOE 413.3B requires contingency at conceptual design.</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="16" t="n"/>
-      <c r="B74" s="16" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="17" t="n"/>
+      <c r="B90" s="17" t="inlineStr">
         <is>
           <t>TOTAL ESTIMATED COST (Base + Contingency)</t>
         </is>
       </c>
-      <c r="C74" s="16" t="n"/>
-      <c r="D74" s="16" t="n"/>
-      <c r="E74" s="16" t="n"/>
-      <c r="F74" s="16">
-        <f>F71+F73</f>
-        <v/>
-      </c>
-      <c r="G74" s="16" t="n"/>
-      <c r="H74" s="16" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="17" t="inlineStr">
+      <c r="F90">
+        <f>F87+F89</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91"/>
+    <row r="92">
+      <c r="A92" s="22" t="inlineStr">
         <is>
           <t>KEY ASSUMPTIONS</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+    <row r="93">
+      <c r="A93" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>Electrical based on Substation 507 option. Substation 502 would add ~$7M to WBS 8.1.</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
+    <row r="94">
+      <c r="A94" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>Circulator cost assumes new procurement ($400k). PEP-II 1.5 MW circulators may be reusable (saves ~$400k).</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
+    <row r="95">
+      <c r="A95" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>2 SSA hot-swap spares included ($623k). Could reduce to 1 (saves $312k) or increase per ops.</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
+    <row r="96">
+      <c r="A96" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>Labor rate: $200/hr burdened (SLAC overhead-inclusive). 1 FTE = 1,740 hrs/yr.</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="17" t="inlineStr">
         <is>
           <t>A5</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>LLRF upgrade is prerequisite and funded separately. LLRF9 controllers, arc detection, waveform buffer, tuner controllers carry over.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>LLRF upgrade is a separate, independent project (not a prerequisite). LLRF9 controllers, arc detection, waveform buffer, and tuner controllers carry over to SSA scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
         <is>
           <t>A6</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>NIP system required per SLAC ESH Chapter 50 (RF &amp; Microwave Safety) for new SSA building with &gt;1 kW RF sources.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="17" t="inlineStr">
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>NIP system required per SLAC ESH Chapter 50 for new SSA building with &gt;1 kW RF sources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>A7</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Decommissioning scope: Marconi K3512S klystron, 2.5 MVA HVPS (oil-insulated transformer, SCR rectifier, crowbar), AFT circulator, WR2100 waveguide/magic tee, lead shielding, HCW cooling. Per SLAC-PUB-10983.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>A8</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>HVPS transformer oil assumed non-PCB. PCB testing required prior to disposal (pre-1979 oil would increase cost significantly).</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>A9</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Scrap/salvage value of removed equipment not credited (conservative). Some copper, lead, steel may have modest scrap value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="22" t="inlineStr">
         <is>
           <t>KEY RISKS</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
+    <row r="104">
+      <c r="A104" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>Interface Chassis on critical path (new SSA-specific design not started). PCB iteration may add 3-6 months.</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
+    <row r="105">
+      <c r="A105" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>PPS redesign scope uncertain. 16-channel SSA safety chain more complex than single-klystron PPS. Safety review timeline unknown.</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
+    <row r="106">
+      <c r="A106" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>NIP system: first SSA installation at SPEAR. No prior RFSP template for this SSA configuration. Safety review may be lengthy.</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
+    <row r="107">
+      <c r="A107" t="inlineStr">
         <is>
           <t>R4</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>EPICS Coordinator software largest untouched scope. Hot-swap logic and N-1 degradation are new SSA-specific requirements.</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
+    <row r="108">
+      <c r="A108" t="inlineStr">
         <is>
           <t>R5</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B108" t="inlineStr">
         <is>
           <t>DOE lab construction costs typically 50-100% higher than commercial. WBS 8.3 building estimate based on F&amp;O prior study ($1.3M); actual cost TBD per CD-1 design.</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
+    <row r="109">
+      <c r="A109" t="inlineStr">
         <is>
           <t>R6</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B109" t="inlineStr">
         <is>
           <t>Limited SPEAR testing windows. Integration constrained to summer shutdowns and brief maintenance periods.</t>
         </is>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Decommissioning: HVPS transformer oil may contain PCBs (pre-1979 equipment from PEP-II era). PCB disposal costs could be 3-5x non-PCB estimate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Decommissioning: Radiological activation of klystron/shielding requires RP survey. If contamination found, disposal costs increase substantially.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
